--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734693</v>
+        <v>122734876</v>
       </c>
       <c r="B20" t="n">
-        <v>90940</v>
+        <v>79843</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,21 +2681,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542111</v>
+        <v>542150</v>
       </c>
       <c r="R20" t="n">
-        <v>7063060</v>
+        <v>7063210</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122734614</v>
+        <v>122734693</v>
       </c>
       <c r="B21" t="n">
-        <v>79878</v>
+        <v>90940</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2779,25 +2779,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542075</v>
+        <v>542111</v>
       </c>
       <c r="R21" t="n">
-        <v>7063031</v>
+        <v>7063060</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122734876</v>
+        <v>122734614</v>
       </c>
       <c r="B22" t="n">
-        <v>79843</v>
+        <v>79878</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542150</v>
+        <v>542075</v>
       </c>
       <c r="R22" t="n">
-        <v>7063210</v>
+        <v>7063031</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -5361,10 +5361,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734998</v>
+        <v>122733497</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5373,31 +5373,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542180</v>
+        <v>541868</v>
       </c>
       <c r="R46" t="n">
-        <v>7063280</v>
+        <v>7063207</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5570,10 +5570,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122733497</v>
+        <v>122734998</v>
       </c>
       <c r="B48" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5582,31 +5582,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541868</v>
+        <v>542180</v>
       </c>
       <c r="R48" t="n">
-        <v>7063207</v>
+        <v>7063280</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6396,10 +6396,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122735414</v>
+        <v>122733400</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>98347</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,31 +6408,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6441,10 +6440,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>542209</v>
+        <v>541821</v>
       </c>
       <c r="R56" t="n">
-        <v>7063388</v>
+        <v>7063185</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6477,11 +6476,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6508,10 +6502,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122733400</v>
+        <v>122735414</v>
       </c>
       <c r="B57" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6520,30 +6514,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6552,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541821</v>
+        <v>542209</v>
       </c>
       <c r="R57" t="n">
-        <v>7063185</v>
+        <v>7063388</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6588,6 +6583,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122734679</v>
+        <v>122733821</v>
       </c>
       <c r="B14" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,27 +2049,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542110</v>
+        <v>541894</v>
       </c>
       <c r="R14" t="n">
-        <v>7063060</v>
+        <v>7063121</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122735437</v>
+        <v>122734549</v>
       </c>
       <c r="B15" t="n">
-        <v>79871</v>
+        <v>56078</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,38 +2152,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542207</v>
+        <v>542051</v>
       </c>
       <c r="R15" t="n">
-        <v>7063420</v>
+        <v>7063037</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2242,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733368</v>
+        <v>122734232</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,43 +2259,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541796</v>
+        <v>541952</v>
       </c>
       <c r="R16" t="n">
-        <v>7063200</v>
+        <v>7063000</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2323,11 +2323,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122735145</v>
+        <v>122734495</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>79751</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,25 +2361,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,10 +2389,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542201</v>
+        <v>542019</v>
       </c>
       <c r="R17" t="n">
-        <v>7063315</v>
+        <v>7063019</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2456,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734661</v>
+        <v>122734679</v>
       </c>
       <c r="B18" t="n">
-        <v>90905</v>
+        <v>56680</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,38 +2463,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542103</v>
+        <v>542110</v>
       </c>
       <c r="R18" t="n">
-        <v>7063058</v>
+        <v>7063060</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734094</v>
+        <v>122733598</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,31 +2570,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541918</v>
+        <v>541891</v>
       </c>
       <c r="R19" t="n">
-        <v>7063050</v>
+        <v>7063227</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734876</v>
+        <v>122733445</v>
       </c>
       <c r="B20" t="n">
-        <v>79843</v>
+        <v>90909</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,25 +2677,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542150</v>
+        <v>541842</v>
       </c>
       <c r="R20" t="n">
-        <v>7063210</v>
+        <v>7063190</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122734693</v>
+        <v>122734127</v>
       </c>
       <c r="B21" t="n">
-        <v>90940</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2783,21 +2783,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542111</v>
+        <v>541949</v>
       </c>
       <c r="R21" t="n">
-        <v>7063060</v>
+        <v>7063047</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122734614</v>
+        <v>122735491</v>
       </c>
       <c r="B22" t="n">
-        <v>79878</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542075</v>
+        <v>542222</v>
       </c>
       <c r="R22" t="n">
-        <v>7063031</v>
+        <v>7063450</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122733746</v>
+        <v>122734884</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2987,39 +2987,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541904</v>
+        <v>542151</v>
       </c>
       <c r="R23" t="n">
-        <v>7063170</v>
+        <v>7063216</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3078,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122734932</v>
+        <v>122734433</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3094,21 +3089,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3118,10 +3113,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542178</v>
+        <v>542016</v>
       </c>
       <c r="R24" t="n">
-        <v>7063224</v>
+        <v>7063029</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3154,11 +3149,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3185,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122734737</v>
+        <v>122734693</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>90944</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3197,43 +3187,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542156</v>
+        <v>542111</v>
       </c>
       <c r="R25" t="n">
-        <v>7063148</v>
+        <v>7063060</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122734232</v>
+        <v>122735514</v>
       </c>
       <c r="B26" t="n">
-        <v>79879</v>
+        <v>79882</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3308,21 +3293,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3332,10 +3317,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541952</v>
+        <v>542225</v>
       </c>
       <c r="R26" t="n">
-        <v>7063000</v>
+        <v>7063451</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3394,10 +3379,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122734709</v>
+        <v>122734184</v>
       </c>
       <c r="B27" t="n">
-        <v>91385</v>
+        <v>97309</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3406,25 +3391,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3434,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542116</v>
+        <v>541962</v>
       </c>
       <c r="R27" t="n">
-        <v>7063065</v>
+        <v>7063054</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3496,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734480</v>
+        <v>122734876</v>
       </c>
       <c r="B28" t="n">
-        <v>90951</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3508,25 +3493,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542012</v>
+        <v>542150</v>
       </c>
       <c r="R28" t="n">
-        <v>7063013</v>
+        <v>7063210</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3598,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733859</v>
+        <v>122734191</v>
       </c>
       <c r="B29" t="n">
-        <v>90940</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3614,21 +3599,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3638,10 +3623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541895</v>
+        <v>541959</v>
       </c>
       <c r="R29" t="n">
-        <v>7063121</v>
+        <v>7063011</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3700,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122734625</v>
+        <v>122735308</v>
       </c>
       <c r="B30" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3740,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542072</v>
+        <v>542199</v>
       </c>
       <c r="R30" t="n">
-        <v>7063043</v>
+        <v>7063368</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3802,10 +3787,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122733611</v>
+        <v>122734589</v>
       </c>
       <c r="B31" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3814,43 +3799,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541894</v>
+        <v>542061</v>
       </c>
       <c r="R31" t="n">
-        <v>7063219</v>
+        <v>7063040</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3909,7 +3889,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122735552</v>
+        <v>122734737</v>
       </c>
       <c r="B32" t="n">
         <v>56688</v>
@@ -3954,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542188</v>
+        <v>542156</v>
       </c>
       <c r="R32" t="n">
-        <v>7063472</v>
+        <v>7063148</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4016,10 +3996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734495</v>
+        <v>122733223</v>
       </c>
       <c r="B33" t="n">
-        <v>79747</v>
+        <v>56688</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4032,34 +4012,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542019</v>
+        <v>541808</v>
       </c>
       <c r="R33" t="n">
-        <v>7063019</v>
+        <v>7063277</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4118,10 +4103,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122735308</v>
+        <v>122740383</v>
       </c>
       <c r="B34" t="n">
-        <v>79843</v>
+        <v>90909</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4130,25 +4115,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4158,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542199</v>
+        <v>542117</v>
       </c>
       <c r="R34" t="n">
-        <v>7063368</v>
+        <v>7063503</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4220,10 +4205,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122734589</v>
+        <v>122734167</v>
       </c>
       <c r="B35" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4260,10 +4245,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542061</v>
+        <v>541962</v>
       </c>
       <c r="R35" t="n">
-        <v>7063040</v>
+        <v>7063054</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4322,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122735491</v>
+        <v>122735524</v>
       </c>
       <c r="B36" t="n">
-        <v>79843</v>
+        <v>79876</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4334,25 +4319,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4362,10 +4347,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542222</v>
+        <v>542224</v>
       </c>
       <c r="R36" t="n">
-        <v>7063450</v>
+        <v>7063455</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4424,10 +4409,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122734549</v>
+        <v>122734570</v>
       </c>
       <c r="B37" t="n">
-        <v>56078</v>
+        <v>90955</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4436,43 +4421,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>206004</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542051</v>
+        <v>542057</v>
       </c>
       <c r="R37" t="n">
-        <v>7063037</v>
+        <v>7063036</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4531,10 +4511,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122733654</v>
+        <v>122734614</v>
       </c>
       <c r="B38" t="n">
-        <v>79714</v>
+        <v>79882</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4543,41 +4523,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>389</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541896</v>
+        <v>542075</v>
       </c>
       <c r="R38" t="n">
-        <v>7063207</v>
+        <v>7063031</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4618,7 +4595,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4637,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122733412</v>
+        <v>122734625</v>
       </c>
       <c r="B39" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4677,10 +4653,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541827</v>
+        <v>542072</v>
       </c>
       <c r="R39" t="n">
-        <v>7063182</v>
+        <v>7063043</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4739,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734433</v>
+        <v>122733412</v>
       </c>
       <c r="B40" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4779,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542016</v>
+        <v>541827</v>
       </c>
       <c r="R40" t="n">
-        <v>7063029</v>
+        <v>7063182</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4841,10 +4817,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122735254</v>
+        <v>122733859</v>
       </c>
       <c r="B41" t="n">
-        <v>79843</v>
+        <v>90944</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,21 +4833,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4881,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542200</v>
+        <v>541895</v>
       </c>
       <c r="R41" t="n">
-        <v>7063362</v>
+        <v>7063121</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4943,10 +4919,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122735193</v>
+        <v>122734998</v>
       </c>
       <c r="B42" t="n">
-        <v>90905</v>
+        <v>57631</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4955,38 +4931,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542209</v>
+        <v>542180</v>
       </c>
       <c r="R42" t="n">
-        <v>7063318</v>
+        <v>7063280</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5045,10 +5026,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122733598</v>
+        <v>122734709</v>
       </c>
       <c r="B43" t="n">
-        <v>56688</v>
+        <v>91389</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5057,43 +5038,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541891</v>
+        <v>542116</v>
       </c>
       <c r="R43" t="n">
-        <v>7063227</v>
+        <v>7063065</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5152,10 +5128,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122734570</v>
+        <v>122733654</v>
       </c>
       <c r="B44" t="n">
-        <v>90951</v>
+        <v>79718</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5164,38 +5140,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1205</v>
+        <v>389</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542057</v>
+        <v>541896</v>
       </c>
       <c r="R44" t="n">
-        <v>7063036</v>
+        <v>7063207</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5236,6 +5215,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5254,10 +5234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122733821</v>
+        <v>122735805</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5270,27 +5250,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5299,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541894</v>
+        <v>542199</v>
       </c>
       <c r="R45" t="n">
-        <v>7063121</v>
+        <v>7063483</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5335,6 +5315,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5361,10 +5346,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122733497</v>
+        <v>122734480</v>
       </c>
       <c r="B46" t="n">
-        <v>56688</v>
+        <v>90955</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5377,39 +5362,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541868</v>
+        <v>542012</v>
       </c>
       <c r="R46" t="n">
-        <v>7063207</v>
+        <v>7063013</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5468,10 +5448,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122734167</v>
+        <v>122735414</v>
       </c>
       <c r="B47" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5484,34 +5464,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541962</v>
+        <v>542209</v>
       </c>
       <c r="R47" t="n">
-        <v>7063054</v>
+        <v>7063388</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5544,6 +5529,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5570,10 +5560,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122734998</v>
+        <v>122733746</v>
       </c>
       <c r="B48" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5582,31 +5572,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542180</v>
+        <v>541904</v>
       </c>
       <c r="R48" t="n">
-        <v>7063280</v>
+        <v>7063170</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5677,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122740383</v>
+        <v>122734559</v>
       </c>
       <c r="B49" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5717,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542117</v>
+        <v>542051</v>
       </c>
       <c r="R49" t="n">
-        <v>7063503</v>
+        <v>7063037</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5779,10 +5769,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122735514</v>
+        <v>122735145</v>
       </c>
       <c r="B50" t="n">
-        <v>79878</v>
+        <v>90944</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5791,25 +5781,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5819,10 +5809,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542225</v>
+        <v>542201</v>
       </c>
       <c r="R50" t="n">
-        <v>7063451</v>
+        <v>7063315</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5881,10 +5871,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122734191</v>
+        <v>122733573</v>
       </c>
       <c r="B51" t="n">
-        <v>79843</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5893,38 +5883,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541959</v>
+        <v>541859</v>
       </c>
       <c r="R51" t="n">
-        <v>7063011</v>
+        <v>7063245</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5983,10 +5978,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122733626</v>
+        <v>122735552</v>
       </c>
       <c r="B52" t="n">
-        <v>79843</v>
+        <v>56688</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5995,38 +5990,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541894</v>
+        <v>542188</v>
       </c>
       <c r="R52" t="n">
-        <v>7063219</v>
+        <v>7063472</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122733223</v>
+        <v>122733623</v>
       </c>
       <c r="B53" t="n">
         <v>56688</v>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541808</v>
+        <v>541894</v>
       </c>
       <c r="R53" t="n">
-        <v>7063277</v>
+        <v>7063219</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122735524</v>
+        <v>122735437</v>
       </c>
       <c r="B54" t="n">
-        <v>79872</v>
+        <v>79875</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542224</v>
+        <v>542207</v>
       </c>
       <c r="R54" t="n">
-        <v>7063455</v>
+        <v>7063420</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6294,10 +6294,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122734127</v>
+        <v>122735193</v>
       </c>
       <c r="B55" t="n">
-        <v>79843</v>
+        <v>90909</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6306,25 +6306,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541949</v>
+        <v>542209</v>
       </c>
       <c r="R55" t="n">
-        <v>7063047</v>
+        <v>7063318</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6396,10 +6396,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122733400</v>
+        <v>122734094</v>
       </c>
       <c r="B56" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,30 +6408,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6440,10 +6441,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541821</v>
+        <v>541918</v>
       </c>
       <c r="R56" t="n">
-        <v>7063185</v>
+        <v>7063050</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6502,10 +6503,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122735414</v>
+        <v>122733497</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6514,31 +6515,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6547,10 +6548,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>542209</v>
+        <v>541868</v>
       </c>
       <c r="R57" t="n">
-        <v>7063388</v>
+        <v>7063207</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6583,11 +6584,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6614,10 +6610,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122733563</v>
+        <v>122733400</v>
       </c>
       <c r="B58" t="n">
-        <v>88299</v>
+        <v>98355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6626,38 +6622,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541868</v>
+        <v>541821</v>
       </c>
       <c r="R58" t="n">
-        <v>7063239</v>
+        <v>7063185</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6716,10 +6716,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122733946</v>
+        <v>122734932</v>
       </c>
       <c r="B59" t="n">
-        <v>74855</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6732,21 +6732,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6756,10 +6756,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541887</v>
+        <v>542178</v>
       </c>
       <c r="R59" t="n">
-        <v>7063133</v>
+        <v>7063224</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6792,6 +6792,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6818,10 +6823,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122733445</v>
+        <v>122733626</v>
       </c>
       <c r="B60" t="n">
-        <v>90905</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6830,25 +6835,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6858,10 +6863,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541842</v>
+        <v>541894</v>
       </c>
       <c r="R60" t="n">
-        <v>7063190</v>
+        <v>7063219</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6920,10 +6925,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122733573</v>
+        <v>122733368</v>
       </c>
       <c r="B61" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6932,31 +6937,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6965,10 +6970,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541859</v>
+        <v>541796</v>
       </c>
       <c r="R61" t="n">
-        <v>7063245</v>
+        <v>7063200</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7001,6 +7006,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7027,10 +7037,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122734884</v>
+        <v>122734661</v>
       </c>
       <c r="B62" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7067,10 +7077,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>542151</v>
+        <v>542103</v>
       </c>
       <c r="R62" t="n">
-        <v>7063216</v>
+        <v>7063058</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7129,10 +7139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122734184</v>
+        <v>122735254</v>
       </c>
       <c r="B63" t="n">
-        <v>97301</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7141,25 +7151,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7169,10 +7179,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541962</v>
+        <v>542200</v>
       </c>
       <c r="R63" t="n">
-        <v>7063054</v>
+        <v>7063362</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7234,7 +7244,7 @@
         <v>122734524</v>
       </c>
       <c r="B64" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7333,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122734559</v>
+        <v>122733946</v>
       </c>
       <c r="B65" t="n">
-        <v>90905</v>
+        <v>74855</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7345,25 +7355,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7373,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542051</v>
+        <v>541887</v>
       </c>
       <c r="R65" t="n">
-        <v>7063037</v>
+        <v>7063133</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7435,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122735805</v>
+        <v>122733563</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>88303</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7451,39 +7461,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>542199</v>
+        <v>541868</v>
       </c>
       <c r="R66" t="n">
-        <v>7063483</v>
+        <v>7063239</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7516,11 +7521,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -4817,10 +4817,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122733859</v>
+        <v>122734998</v>
       </c>
       <c r="B41" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4833,34 +4833,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541895</v>
+        <v>542180</v>
       </c>
       <c r="R41" t="n">
-        <v>7063121</v>
+        <v>7063280</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4919,10 +4924,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734998</v>
+        <v>122733859</v>
       </c>
       <c r="B42" t="n">
-        <v>57631</v>
+        <v>90944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4935,39 +4940,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542180</v>
+        <v>541895</v>
       </c>
       <c r="R42" t="n">
-        <v>7063280</v>
+        <v>7063121</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122733821</v>
+        <v>122734693</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,39 +2049,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541894</v>
+        <v>542111</v>
       </c>
       <c r="R14" t="n">
-        <v>7063121</v>
+        <v>7063060</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2140,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122734549</v>
+        <v>122735414</v>
       </c>
       <c r="B15" t="n">
-        <v>56078</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,27 +2151,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542051</v>
+        <v>542209</v>
       </c>
       <c r="R15" t="n">
-        <v>7063037</v>
+        <v>7063388</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,6 +2216,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122734232</v>
+        <v>122733573</v>
       </c>
       <c r="B16" t="n">
-        <v>79883</v>
+        <v>56688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,34 +2263,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541952</v>
+        <v>541859</v>
       </c>
       <c r="R16" t="n">
-        <v>7063000</v>
+        <v>7063245</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2349,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122734495</v>
+        <v>122733223</v>
       </c>
       <c r="B17" t="n">
-        <v>79751</v>
+        <v>56688</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,34 +2370,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542019</v>
+        <v>541808</v>
       </c>
       <c r="R17" t="n">
-        <v>7063019</v>
+        <v>7063277</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2451,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734679</v>
+        <v>122734737</v>
       </c>
       <c r="B18" t="n">
-        <v>56680</v>
+        <v>56688</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,25 +2473,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2496,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542110</v>
+        <v>542156</v>
       </c>
       <c r="R18" t="n">
-        <v>7063060</v>
+        <v>7063148</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2558,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122733598</v>
+        <v>122734127</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,43 +2580,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541891</v>
+        <v>541949</v>
       </c>
       <c r="R19" t="n">
-        <v>7063227</v>
+        <v>7063047</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2665,7 +2670,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122733445</v>
+        <v>122734661</v>
       </c>
       <c r="B20" t="n">
         <v>90909</v>
@@ -2705,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541842</v>
+        <v>542103</v>
       </c>
       <c r="R20" t="n">
-        <v>7063190</v>
+        <v>7063058</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2767,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122734127</v>
+        <v>122735524</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2779,25 +2784,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2807,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541949</v>
+        <v>542224</v>
       </c>
       <c r="R21" t="n">
-        <v>7063047</v>
+        <v>7063455</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2869,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122735491</v>
+        <v>122735805</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2885,34 +2890,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542222</v>
+        <v>542199</v>
       </c>
       <c r="R22" t="n">
-        <v>7063450</v>
+        <v>7063483</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2945,6 +2955,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2971,10 +2986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122734884</v>
+        <v>122733400</v>
       </c>
       <c r="B23" t="n">
-        <v>90909</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2983,38 +2998,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542151</v>
+        <v>541821</v>
       </c>
       <c r="R23" t="n">
-        <v>7063216</v>
+        <v>7063185</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3073,10 +3092,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122734433</v>
+        <v>122740383</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,25 +3104,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3113,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542016</v>
+        <v>542117</v>
       </c>
       <c r="R24" t="n">
-        <v>7063029</v>
+        <v>7063503</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3175,10 +3194,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122734693</v>
+        <v>122734589</v>
       </c>
       <c r="B25" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,21 +3210,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3215,10 +3234,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542111</v>
+        <v>542061</v>
       </c>
       <c r="R25" t="n">
-        <v>7063060</v>
+        <v>7063040</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3277,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122735514</v>
+        <v>122733563</v>
       </c>
       <c r="B26" t="n">
-        <v>79882</v>
+        <v>88303</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3289,25 +3308,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3317,10 +3336,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542225</v>
+        <v>541868</v>
       </c>
       <c r="R26" t="n">
-        <v>7063451</v>
+        <v>7063239</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3379,10 +3398,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122734184</v>
+        <v>122734709</v>
       </c>
       <c r="B27" t="n">
-        <v>97309</v>
+        <v>91389</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,25 +3410,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3419,10 +3438,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541962</v>
+        <v>542116</v>
       </c>
       <c r="R27" t="n">
-        <v>7063054</v>
+        <v>7063065</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3481,10 +3500,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734876</v>
+        <v>122734614</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3493,25 +3512,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3521,10 +3540,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542150</v>
+        <v>542075</v>
       </c>
       <c r="R28" t="n">
-        <v>7063210</v>
+        <v>7063031</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3583,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122734191</v>
+        <v>122733497</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,38 +3614,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541959</v>
+        <v>541868</v>
       </c>
       <c r="R29" t="n">
-        <v>7063011</v>
+        <v>7063207</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3685,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122735308</v>
+        <v>122733445</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3697,25 +3721,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3725,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542199</v>
+        <v>541842</v>
       </c>
       <c r="R30" t="n">
-        <v>7063368</v>
+        <v>7063190</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3787,7 +3811,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122734589</v>
+        <v>122735491</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -3827,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542061</v>
+        <v>542222</v>
       </c>
       <c r="R31" t="n">
-        <v>7063040</v>
+        <v>7063450</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3889,10 +3913,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122734737</v>
+        <v>122733368</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3901,31 +3925,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3934,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542156</v>
+        <v>541796</v>
       </c>
       <c r="R32" t="n">
-        <v>7063148</v>
+        <v>7063200</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3970,6 +3994,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3996,10 +4025,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122733223</v>
+        <v>122734625</v>
       </c>
       <c r="B33" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4008,43 +4037,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541808</v>
+        <v>542072</v>
       </c>
       <c r="R33" t="n">
-        <v>7063277</v>
+        <v>7063043</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4103,10 +4127,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122740383</v>
+        <v>122734167</v>
       </c>
       <c r="B34" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4115,25 +4139,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4143,10 +4167,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542117</v>
+        <v>541962</v>
       </c>
       <c r="R34" t="n">
-        <v>7063503</v>
+        <v>7063054</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4205,10 +4229,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122734167</v>
+        <v>122735437</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>79875</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4217,25 +4241,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4245,10 +4269,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541962</v>
+        <v>542207</v>
       </c>
       <c r="R35" t="n">
-        <v>7063054</v>
+        <v>7063420</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4307,10 +4331,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122735524</v>
+        <v>122734495</v>
       </c>
       <c r="B36" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4323,21 +4347,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4347,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542224</v>
+        <v>542019</v>
       </c>
       <c r="R36" t="n">
-        <v>7063455</v>
+        <v>7063019</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4409,10 +4433,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122734570</v>
+        <v>122735308</v>
       </c>
       <c r="B37" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,25 +4445,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4449,10 +4473,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542057</v>
+        <v>542199</v>
       </c>
       <c r="R37" t="n">
-        <v>7063036</v>
+        <v>7063368</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4511,10 +4535,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122734614</v>
+        <v>122735254</v>
       </c>
       <c r="B38" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4523,25 +4547,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4551,10 +4575,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542075</v>
+        <v>542200</v>
       </c>
       <c r="R38" t="n">
-        <v>7063031</v>
+        <v>7063362</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4613,10 +4637,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122734625</v>
+        <v>122734232</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4625,25 +4649,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4653,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542072</v>
+        <v>541952</v>
       </c>
       <c r="R39" t="n">
-        <v>7063043</v>
+        <v>7063000</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4715,10 +4739,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122733412</v>
+        <v>122734184</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>97309</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4727,25 +4751,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4755,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541827</v>
+        <v>541962</v>
       </c>
       <c r="R40" t="n">
-        <v>7063182</v>
+        <v>7063054</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4924,10 +4948,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733859</v>
+        <v>122734480</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>90955</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,25 +4960,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4964,10 +4988,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541895</v>
+        <v>542012</v>
       </c>
       <c r="R42" t="n">
-        <v>7063121</v>
+        <v>7063013</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5026,10 +5050,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734709</v>
+        <v>122734433</v>
       </c>
       <c r="B43" t="n">
-        <v>91389</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5038,25 +5062,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5066,10 +5090,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542116</v>
+        <v>542016</v>
       </c>
       <c r="R43" t="n">
-        <v>7063065</v>
+        <v>7063029</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5128,10 +5152,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122733654</v>
+        <v>122734570</v>
       </c>
       <c r="B44" t="n">
-        <v>79718</v>
+        <v>90955</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5140,41 +5164,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>389</v>
+        <v>1205</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541896</v>
+        <v>542057</v>
       </c>
       <c r="R44" t="n">
-        <v>7063207</v>
+        <v>7063036</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5215,7 +5236,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5234,10 +5254,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122735805</v>
+        <v>122733946</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>74855</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5250,39 +5270,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542199</v>
+        <v>541887</v>
       </c>
       <c r="R45" t="n">
-        <v>7063483</v>
+        <v>7063133</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5315,11 +5330,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5346,10 +5356,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734480</v>
+        <v>122734524</v>
       </c>
       <c r="B46" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5358,25 +5368,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5396,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542012</v>
+        <v>542051</v>
       </c>
       <c r="R46" t="n">
-        <v>7063013</v>
+        <v>7063037</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5448,10 +5458,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122735414</v>
+        <v>122735145</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,39 +5474,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542209</v>
+        <v>542201</v>
       </c>
       <c r="R47" t="n">
-        <v>7063388</v>
+        <v>7063315</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5529,11 +5534,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5560,10 +5560,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122733746</v>
+        <v>122733859</v>
       </c>
       <c r="B48" t="n">
-        <v>56688</v>
+        <v>90944</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5572,43 +5572,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541904</v>
+        <v>541895</v>
       </c>
       <c r="R48" t="n">
-        <v>7063170</v>
+        <v>7063121</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5667,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122734559</v>
+        <v>122733412</v>
       </c>
       <c r="B49" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5679,25 +5674,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542051</v>
+        <v>541827</v>
       </c>
       <c r="R49" t="n">
-        <v>7063037</v>
+        <v>7063182</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5769,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122735145</v>
+        <v>122735193</v>
       </c>
       <c r="B50" t="n">
-        <v>90944</v>
+        <v>90909</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5781,25 +5776,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5809,10 +5804,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542201</v>
+        <v>542209</v>
       </c>
       <c r="R50" t="n">
-        <v>7063315</v>
+        <v>7063318</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5871,10 +5866,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122733573</v>
+        <v>122735514</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>79882</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5887,39 +5882,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541859</v>
+        <v>542225</v>
       </c>
       <c r="R51" t="n">
-        <v>7063245</v>
+        <v>7063451</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5978,7 +5968,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122735552</v>
+        <v>122733746</v>
       </c>
       <c r="B52" t="n">
         <v>56688</v>
@@ -6023,10 +6013,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542188</v>
+        <v>541904</v>
       </c>
       <c r="R52" t="n">
-        <v>7063472</v>
+        <v>7063170</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6085,7 +6075,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122733623</v>
+        <v>122733598</v>
       </c>
       <c r="B53" t="n">
         <v>56688</v>
@@ -6130,10 +6120,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541894</v>
+        <v>541891</v>
       </c>
       <c r="R53" t="n">
-        <v>7063219</v>
+        <v>7063227</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6192,10 +6182,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122735437</v>
+        <v>122733654</v>
       </c>
       <c r="B54" t="n">
-        <v>79875</v>
+        <v>79718</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6204,38 +6194,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>389</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542207</v>
+        <v>541896</v>
       </c>
       <c r="R54" t="n">
-        <v>7063420</v>
+        <v>7063207</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6276,6 +6269,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6294,10 +6288,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122735193</v>
+        <v>122734876</v>
       </c>
       <c r="B55" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6306,25 +6300,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6334,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542209</v>
+        <v>542150</v>
       </c>
       <c r="R55" t="n">
-        <v>7063318</v>
+        <v>7063210</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6396,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122734094</v>
+        <v>122733626</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6412,39 +6406,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541918</v>
+        <v>541894</v>
       </c>
       <c r="R56" t="n">
-        <v>7063050</v>
+        <v>7063219</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6503,10 +6492,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122733497</v>
+        <v>122734094</v>
       </c>
       <c r="B57" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6515,31 +6504,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6548,10 +6537,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541868</v>
+        <v>541918</v>
       </c>
       <c r="R57" t="n">
-        <v>7063207</v>
+        <v>7063050</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6610,10 +6599,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122733400</v>
+        <v>122733623</v>
       </c>
       <c r="B58" t="n">
-        <v>98355</v>
+        <v>56688</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6622,30 +6611,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6654,10 +6644,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541821</v>
+        <v>541894</v>
       </c>
       <c r="R58" t="n">
-        <v>7063185</v>
+        <v>7063219</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6716,10 +6706,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122734932</v>
+        <v>122734884</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6728,25 +6718,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6756,10 +6746,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542178</v>
+        <v>542151</v>
       </c>
       <c r="R59" t="n">
-        <v>7063224</v>
+        <v>7063216</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6792,11 +6782,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6823,10 +6808,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122733626</v>
+        <v>122733821</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6839,24 +6824,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
@@ -6866,7 +6856,7 @@
         <v>541894</v>
       </c>
       <c r="R60" t="n">
-        <v>7063219</v>
+        <v>7063121</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6925,10 +6915,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122733368</v>
+        <v>122734191</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6941,39 +6931,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541796</v>
+        <v>541959</v>
       </c>
       <c r="R61" t="n">
-        <v>7063200</v>
+        <v>7063011</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7006,11 +6991,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7037,10 +7017,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122734661</v>
+        <v>122734679</v>
       </c>
       <c r="B62" t="n">
-        <v>90909</v>
+        <v>56680</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7049,38 +7029,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>542103</v>
+        <v>542110</v>
       </c>
       <c r="R62" t="n">
-        <v>7063058</v>
+        <v>7063060</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7139,10 +7124,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122735254</v>
+        <v>122734549</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>56078</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7155,34 +7140,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542200</v>
+        <v>542051</v>
       </c>
       <c r="R63" t="n">
-        <v>7063362</v>
+        <v>7063037</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7241,10 +7231,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122734524</v>
+        <v>122734559</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7253,25 +7243,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7343,10 +7333,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122733946</v>
+        <v>122734932</v>
       </c>
       <c r="B65" t="n">
-        <v>74855</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7359,21 +7349,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7383,10 +7373,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541887</v>
+        <v>542178</v>
       </c>
       <c r="R65" t="n">
-        <v>7063133</v>
+        <v>7063224</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7419,6 +7409,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7445,10 +7440,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122733563</v>
+        <v>122735552</v>
       </c>
       <c r="B66" t="n">
-        <v>88303</v>
+        <v>56688</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7457,38 +7452,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541868</v>
+        <v>542188</v>
       </c>
       <c r="R66" t="n">
-        <v>7063239</v>
+        <v>7063472</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122734693</v>
+        <v>122733223</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,38 +2045,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542111</v>
+        <v>541808</v>
       </c>
       <c r="R14" t="n">
-        <v>7063060</v>
+        <v>7063277</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2135,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122735414</v>
+        <v>122734679</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,16 +2156,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2171,7 +2176,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2180,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542209</v>
+        <v>542110</v>
       </c>
       <c r="R15" t="n">
-        <v>7063388</v>
+        <v>7063060</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2216,11 +2221,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733573</v>
+        <v>122733563</v>
       </c>
       <c r="B16" t="n">
-        <v>56688</v>
+        <v>88303</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,43 +2259,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541859</v>
+        <v>541868</v>
       </c>
       <c r="R16" t="n">
-        <v>7063245</v>
+        <v>7063239</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2354,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733223</v>
+        <v>122734167</v>
       </c>
       <c r="B17" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,43 +2361,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541808</v>
+        <v>541962</v>
       </c>
       <c r="R17" t="n">
-        <v>7063277</v>
+        <v>7063054</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2461,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734737</v>
+        <v>122734614</v>
       </c>
       <c r="B18" t="n">
-        <v>56688</v>
+        <v>79882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,39 +2467,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542156</v>
+        <v>542075</v>
       </c>
       <c r="R18" t="n">
-        <v>7063148</v>
+        <v>7063031</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2568,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734127</v>
+        <v>122734480</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>90955</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,25 +2565,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541949</v>
+        <v>542012</v>
       </c>
       <c r="R19" t="n">
-        <v>7063047</v>
+        <v>7063013</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,7 +2655,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734661</v>
+        <v>122734884</v>
       </c>
       <c r="B20" t="n">
         <v>90909</v>
@@ -2710,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542103</v>
+        <v>542151</v>
       </c>
       <c r="R20" t="n">
-        <v>7063058</v>
+        <v>7063216</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2772,10 +2757,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122735524</v>
+        <v>122735193</v>
       </c>
       <c r="B21" t="n">
-        <v>79876</v>
+        <v>90909</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2773,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2812,10 +2797,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542224</v>
+        <v>542209</v>
       </c>
       <c r="R21" t="n">
-        <v>7063455</v>
+        <v>7063318</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2874,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122735805</v>
+        <v>122733626</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2890,39 +2875,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542199</v>
+        <v>541894</v>
       </c>
       <c r="R22" t="n">
-        <v>7063483</v>
+        <v>7063219</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2955,11 +2935,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2986,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122733400</v>
+        <v>122734998</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2998,30 +2973,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3030,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541821</v>
+        <v>542180</v>
       </c>
       <c r="R23" t="n">
-        <v>7063185</v>
+        <v>7063280</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3092,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122740383</v>
+        <v>122735514</v>
       </c>
       <c r="B24" t="n">
-        <v>90909</v>
+        <v>79882</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3108,21 +3084,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3132,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542117</v>
+        <v>542225</v>
       </c>
       <c r="R24" t="n">
-        <v>7063503</v>
+        <v>7063451</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3194,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122734589</v>
+        <v>122735437</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>79875</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3206,25 +3182,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3234,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542061</v>
+        <v>542207</v>
       </c>
       <c r="R25" t="n">
-        <v>7063040</v>
+        <v>7063420</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3296,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122733563</v>
+        <v>122733400</v>
       </c>
       <c r="B26" t="n">
-        <v>88303</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3308,38 +3284,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541868</v>
+        <v>541821</v>
       </c>
       <c r="R26" t="n">
-        <v>7063239</v>
+        <v>7063185</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3398,10 +3378,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122734709</v>
+        <v>122733368</v>
       </c>
       <c r="B27" t="n">
-        <v>91389</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3410,38 +3390,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542116</v>
+        <v>541796</v>
       </c>
       <c r="R27" t="n">
-        <v>7063065</v>
+        <v>7063200</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3474,6 +3459,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,10 +3490,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734614</v>
+        <v>122734737</v>
       </c>
       <c r="B28" t="n">
-        <v>79882</v>
+        <v>56688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3516,34 +3506,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542075</v>
+        <v>542156</v>
       </c>
       <c r="R28" t="n">
-        <v>7063031</v>
+        <v>7063148</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3602,7 +3597,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733497</v>
+        <v>122733611</v>
       </c>
       <c r="B29" t="n">
         <v>56688</v>
@@ -3647,10 +3642,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541868</v>
+        <v>541894</v>
       </c>
       <c r="R29" t="n">
-        <v>7063207</v>
+        <v>7063219</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3709,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733445</v>
+        <v>122734570</v>
       </c>
       <c r="B30" t="n">
-        <v>90909</v>
+        <v>90955</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3725,21 +3720,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3749,10 +3744,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541842</v>
+        <v>542057</v>
       </c>
       <c r="R30" t="n">
-        <v>7063190</v>
+        <v>7063036</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3811,10 +3806,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122735491</v>
+        <v>122734932</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3827,21 +3822,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3851,10 +3846,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542222</v>
+        <v>542178</v>
       </c>
       <c r="R31" t="n">
-        <v>7063450</v>
+        <v>7063224</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3887,6 +3882,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3913,7 +3913,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122733368</v>
+        <v>122735414</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3949,7 +3949,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541796</v>
+        <v>542209</v>
       </c>
       <c r="R32" t="n">
-        <v>7063200</v>
+        <v>7063388</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, gammal tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4025,10 +4025,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734625</v>
+        <v>122734661</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4037,25 +4037,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542072</v>
+        <v>542103</v>
       </c>
       <c r="R33" t="n">
-        <v>7063043</v>
+        <v>7063058</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4127,7 +4127,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734167</v>
+        <v>122734625</v>
       </c>
       <c r="B34" t="n">
         <v>79847</v>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541962</v>
+        <v>542072</v>
       </c>
       <c r="R34" t="n">
-        <v>7063054</v>
+        <v>7063043</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122735437</v>
+        <v>122733598</v>
       </c>
       <c r="B35" t="n">
-        <v>79875</v>
+        <v>56688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,34 +4245,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542207</v>
+        <v>541891</v>
       </c>
       <c r="R35" t="n">
-        <v>7063420</v>
+        <v>7063227</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4331,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122734495</v>
+        <v>122733445</v>
       </c>
       <c r="B36" t="n">
-        <v>79751</v>
+        <v>90909</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,21 +4352,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4371,10 +4376,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542019</v>
+        <v>541842</v>
       </c>
       <c r="R36" t="n">
-        <v>7063019</v>
+        <v>7063190</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4433,10 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122735308</v>
+        <v>122734559</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4445,25 +4450,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4473,10 +4478,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542199</v>
+        <v>542051</v>
       </c>
       <c r="R37" t="n">
-        <v>7063368</v>
+        <v>7063037</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4535,7 +4540,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122735254</v>
+        <v>122735491</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4575,10 +4580,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542200</v>
+        <v>542222</v>
       </c>
       <c r="R38" t="n">
-        <v>7063362</v>
+        <v>7063450</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4637,10 +4642,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122734232</v>
+        <v>122733497</v>
       </c>
       <c r="B39" t="n">
-        <v>79883</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4653,34 +4658,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541952</v>
+        <v>541868</v>
       </c>
       <c r="R39" t="n">
-        <v>7063000</v>
+        <v>7063207</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4739,10 +4749,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734184</v>
+        <v>122733746</v>
       </c>
       <c r="B40" t="n">
-        <v>97309</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,34 +4765,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541962</v>
+        <v>541904</v>
       </c>
       <c r="R40" t="n">
-        <v>7063054</v>
+        <v>7063170</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4841,10 +4856,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734998</v>
+        <v>122735805</v>
       </c>
       <c r="B41" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,27 +4872,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4886,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542180</v>
+        <v>542199</v>
       </c>
       <c r="R41" t="n">
-        <v>7063280</v>
+        <v>7063483</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4922,6 +4937,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4948,10 +4968,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734480</v>
+        <v>122733946</v>
       </c>
       <c r="B42" t="n">
-        <v>90955</v>
+        <v>74855</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4960,25 +4980,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1205</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4988,10 +5008,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542012</v>
+        <v>541887</v>
       </c>
       <c r="R42" t="n">
-        <v>7063013</v>
+        <v>7063133</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5050,7 +5070,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734433</v>
+        <v>122734524</v>
       </c>
       <c r="B43" t="n">
         <v>79847</v>
@@ -5090,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542016</v>
+        <v>542051</v>
       </c>
       <c r="R43" t="n">
-        <v>7063029</v>
+        <v>7063037</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5152,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122734570</v>
+        <v>122733573</v>
       </c>
       <c r="B44" t="n">
-        <v>90955</v>
+        <v>56688</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5168,34 +5188,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542057</v>
+        <v>541859</v>
       </c>
       <c r="R44" t="n">
-        <v>7063036</v>
+        <v>7063245</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5254,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122733946</v>
+        <v>122735254</v>
       </c>
       <c r="B45" t="n">
-        <v>74855</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5270,21 +5295,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5294,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541887</v>
+        <v>542200</v>
       </c>
       <c r="R45" t="n">
-        <v>7063133</v>
+        <v>7063362</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5356,7 +5381,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734524</v>
+        <v>122734191</v>
       </c>
       <c r="B46" t="n">
         <v>79847</v>
@@ -5396,10 +5421,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542051</v>
+        <v>541959</v>
       </c>
       <c r="R46" t="n">
-        <v>7063037</v>
+        <v>7063011</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5458,10 +5483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122735145</v>
+        <v>122734589</v>
       </c>
       <c r="B47" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5474,21 +5499,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5498,10 +5523,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542201</v>
+        <v>542061</v>
       </c>
       <c r="R47" t="n">
-        <v>7063315</v>
+        <v>7063040</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5560,10 +5585,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122733859</v>
+        <v>122733821</v>
       </c>
       <c r="B48" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5576,31 +5601,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541895</v>
+        <v>541894</v>
       </c>
       <c r="R48" t="n">
         <v>7063121</v>
@@ -5662,10 +5692,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122733412</v>
+        <v>122734232</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5674,25 +5704,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5702,10 +5732,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541827</v>
+        <v>541952</v>
       </c>
       <c r="R49" t="n">
-        <v>7063182</v>
+        <v>7063000</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5764,10 +5794,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122735193</v>
+        <v>122735145</v>
       </c>
       <c r="B50" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5776,25 +5806,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5834,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542209</v>
+        <v>542201</v>
       </c>
       <c r="R50" t="n">
-        <v>7063318</v>
+        <v>7063315</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5866,10 +5896,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122735514</v>
+        <v>122735552</v>
       </c>
       <c r="B51" t="n">
-        <v>79882</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5882,34 +5912,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542225</v>
+        <v>542188</v>
       </c>
       <c r="R51" t="n">
-        <v>7063451</v>
+        <v>7063472</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5968,10 +6003,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122733746</v>
+        <v>122740383</v>
       </c>
       <c r="B52" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5984,39 +6019,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541904</v>
+        <v>542117</v>
       </c>
       <c r="R52" t="n">
-        <v>7063170</v>
+        <v>7063503</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6075,10 +6105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122733598</v>
+        <v>122735308</v>
       </c>
       <c r="B53" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6087,43 +6117,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541891</v>
+        <v>542199</v>
       </c>
       <c r="R53" t="n">
-        <v>7063227</v>
+        <v>7063368</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6182,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122733654</v>
+        <v>122734094</v>
       </c>
       <c r="B54" t="n">
-        <v>79718</v>
+        <v>57494</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,41 +6219,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>389</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541896</v>
+        <v>541918</v>
       </c>
       <c r="R54" t="n">
-        <v>7063207</v>
+        <v>7063050</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6269,7 +6296,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6288,10 +6314,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122734876</v>
+        <v>122734549</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>56078</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6304,34 +6330,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542150</v>
+        <v>542051</v>
       </c>
       <c r="R55" t="n">
-        <v>7063210</v>
+        <v>7063037</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6390,7 +6421,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122733626</v>
+        <v>122733412</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6430,10 +6461,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541894</v>
+        <v>541827</v>
       </c>
       <c r="R56" t="n">
-        <v>7063219</v>
+        <v>7063182</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6492,10 +6523,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734094</v>
+        <v>122734693</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>90944</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6508,39 +6539,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541918</v>
+        <v>542111</v>
       </c>
       <c r="R57" t="n">
-        <v>7063050</v>
+        <v>7063060</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6599,10 +6625,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122733623</v>
+        <v>122735524</v>
       </c>
       <c r="B58" t="n">
-        <v>56688</v>
+        <v>79876</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6615,39 +6641,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541894</v>
+        <v>542224</v>
       </c>
       <c r="R58" t="n">
-        <v>7063219</v>
+        <v>7063455</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6706,10 +6727,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122734884</v>
+        <v>122734876</v>
       </c>
       <c r="B59" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6718,25 +6739,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6746,10 +6767,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542151</v>
+        <v>542150</v>
       </c>
       <c r="R59" t="n">
-        <v>7063216</v>
+        <v>7063210</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6808,10 +6829,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122733821</v>
+        <v>122734495</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6820,43 +6841,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541894</v>
+        <v>542019</v>
       </c>
       <c r="R60" t="n">
-        <v>7063121</v>
+        <v>7063019</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6915,10 +6931,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122734191</v>
+        <v>122734184</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>97311</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6927,25 +6943,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6955,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541959</v>
+        <v>541962</v>
       </c>
       <c r="R61" t="n">
-        <v>7063011</v>
+        <v>7063054</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7017,10 +7033,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122734679</v>
+        <v>122733859</v>
       </c>
       <c r="B62" t="n">
-        <v>56680</v>
+        <v>90944</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7033,39 +7049,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>542110</v>
+        <v>541895</v>
       </c>
       <c r="R62" t="n">
-        <v>7063060</v>
+        <v>7063121</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7124,10 +7135,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122734549</v>
+        <v>122734709</v>
       </c>
       <c r="B63" t="n">
-        <v>56078</v>
+        <v>91389</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7136,43 +7147,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>206004</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542051</v>
+        <v>542116</v>
       </c>
       <c r="R63" t="n">
-        <v>7063037</v>
+        <v>7063065</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7231,10 +7237,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122734559</v>
+        <v>122733654</v>
       </c>
       <c r="B64" t="n">
-        <v>90909</v>
+        <v>79718</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7243,38 +7249,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>389</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542051</v>
+        <v>541896</v>
       </c>
       <c r="R64" t="n">
-        <v>7063037</v>
+        <v>7063207</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7315,6 +7324,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7333,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122734932</v>
+        <v>122734127</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7349,21 +7359,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7373,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542178</v>
+        <v>541949</v>
       </c>
       <c r="R65" t="n">
-        <v>7063224</v>
+        <v>7063047</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7409,11 +7419,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7440,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122735552</v>
+        <v>122734433</v>
       </c>
       <c r="B66" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7452,43 +7457,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>542188</v>
+        <v>542016</v>
       </c>
       <c r="R66" t="n">
-        <v>7063472</v>
+        <v>7063029</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734614</v>
+        <v>122734998</v>
       </c>
       <c r="B18" t="n">
-        <v>79882</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,38 +2463,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542075</v>
+        <v>542180</v>
       </c>
       <c r="R18" t="n">
-        <v>7063031</v>
+        <v>7063280</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2859,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122733626</v>
+        <v>122734614</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,25 +2876,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2899,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541894</v>
+        <v>542075</v>
       </c>
       <c r="R22" t="n">
-        <v>7063219</v>
+        <v>7063031</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2961,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122734998</v>
+        <v>122733626</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,39 +2982,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542180</v>
+        <v>541894</v>
       </c>
       <c r="R23" t="n">
-        <v>7063280</v>
+        <v>7063219</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122735514</v>
+        <v>122733400</v>
       </c>
       <c r="B24" t="n">
-        <v>79882</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,38 +3080,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542225</v>
+        <v>541821</v>
       </c>
       <c r="R24" t="n">
-        <v>7063451</v>
+        <v>7063185</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3170,10 +3174,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122735437</v>
+        <v>122735514</v>
       </c>
       <c r="B25" t="n">
-        <v>79875</v>
+        <v>79882</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,21 +3190,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3210,10 +3214,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542207</v>
+        <v>542225</v>
       </c>
       <c r="R25" t="n">
-        <v>7063420</v>
+        <v>7063451</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3272,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122733400</v>
+        <v>122735437</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>79875</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3284,42 +3288,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541821</v>
+        <v>542207</v>
       </c>
       <c r="R26" t="n">
-        <v>7063185</v>
+        <v>7063420</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734737</v>
+        <v>122734570</v>
       </c>
       <c r="B28" t="n">
-        <v>56688</v>
+        <v>90955</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,39 +3506,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542156</v>
+        <v>542057</v>
       </c>
       <c r="R28" t="n">
-        <v>7063148</v>
+        <v>7063036</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3597,7 +3592,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733611</v>
+        <v>122734737</v>
       </c>
       <c r="B29" t="n">
         <v>56688</v>
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541894</v>
+        <v>542156</v>
       </c>
       <c r="R29" t="n">
-        <v>7063219</v>
+        <v>7063148</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3704,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122734570</v>
+        <v>122733611</v>
       </c>
       <c r="B30" t="n">
-        <v>90955</v>
+        <v>56688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3720,34 +3715,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542057</v>
+        <v>541894</v>
       </c>
       <c r="R30" t="n">
-        <v>7063036</v>
+        <v>7063219</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734191</v>
+        <v>122733821</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5397,34 +5397,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541959</v>
+        <v>541894</v>
       </c>
       <c r="R46" t="n">
-        <v>7063011</v>
+        <v>7063121</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5483,10 +5488,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122734589</v>
+        <v>122734232</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5495,25 +5500,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542061</v>
+        <v>541952</v>
       </c>
       <c r="R47" t="n">
-        <v>7063040</v>
+        <v>7063000</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5585,10 +5590,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122733821</v>
+        <v>122734191</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5601,39 +5606,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541894</v>
+        <v>541959</v>
       </c>
       <c r="R48" t="n">
-        <v>7063121</v>
+        <v>7063011</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122734232</v>
+        <v>122734589</v>
       </c>
       <c r="B49" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5704,25 +5704,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541952</v>
+        <v>542061</v>
       </c>
       <c r="R49" t="n">
-        <v>7063000</v>
+        <v>7063040</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122735552</v>
+        <v>122740383</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5912,39 +5912,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542188</v>
+        <v>542117</v>
       </c>
       <c r="R51" t="n">
-        <v>7063472</v>
+        <v>7063503</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6003,10 +5998,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122740383</v>
+        <v>122735308</v>
       </c>
       <c r="B52" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6015,25 +6010,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6043,10 +6038,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542117</v>
+        <v>542199</v>
       </c>
       <c r="R52" t="n">
-        <v>7063503</v>
+        <v>7063368</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6105,10 +6100,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122735308</v>
+        <v>122734094</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6121,34 +6116,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542199</v>
+        <v>541918</v>
       </c>
       <c r="R53" t="n">
-        <v>7063368</v>
+        <v>7063050</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122734094</v>
+        <v>122735552</v>
       </c>
       <c r="B54" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6219,31 +6219,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541918</v>
+        <v>542188</v>
       </c>
       <c r="R54" t="n">
-        <v>7063050</v>
+        <v>7063472</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6625,10 +6625,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122735524</v>
+        <v>122734184</v>
       </c>
       <c r="B58" t="n">
-        <v>79876</v>
+        <v>97311</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6641,21 +6641,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542224</v>
+        <v>541962</v>
       </c>
       <c r="R58" t="n">
-        <v>7063455</v>
+        <v>7063054</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6727,10 +6727,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122734876</v>
+        <v>122735524</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6739,25 +6739,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542150</v>
+        <v>542224</v>
       </c>
       <c r="R59" t="n">
-        <v>7063210</v>
+        <v>7063455</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6829,10 +6829,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122734495</v>
+        <v>122734876</v>
       </c>
       <c r="B60" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6841,25 +6841,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542019</v>
+        <v>542150</v>
       </c>
       <c r="R60" t="n">
-        <v>7063019</v>
+        <v>7063210</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122734184</v>
+        <v>122734495</v>
       </c>
       <c r="B61" t="n">
-        <v>97311</v>
+        <v>79751</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6947,21 +6947,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541962</v>
+        <v>542019</v>
       </c>
       <c r="R61" t="n">
-        <v>7063054</v>
+        <v>7063019</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -5896,10 +5896,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122740383</v>
+        <v>122735552</v>
       </c>
       <c r="B51" t="n">
-        <v>90909</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5912,34 +5912,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542117</v>
+        <v>542188</v>
       </c>
       <c r="R51" t="n">
-        <v>7063503</v>
+        <v>7063472</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5998,10 +6003,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122735308</v>
+        <v>122740383</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,25 +6015,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6038,10 +6043,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542199</v>
+        <v>542117</v>
       </c>
       <c r="R52" t="n">
-        <v>7063368</v>
+        <v>7063503</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6100,10 +6105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122734094</v>
+        <v>122735308</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6116,39 +6121,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541918</v>
+        <v>542199</v>
       </c>
       <c r="R53" t="n">
-        <v>7063050</v>
+        <v>7063368</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122735552</v>
+        <v>122734094</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6219,31 +6219,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542188</v>
+        <v>541918</v>
       </c>
       <c r="R54" t="n">
-        <v>7063472</v>
+        <v>7063050</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6625,10 +6625,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122734184</v>
+        <v>122735524</v>
       </c>
       <c r="B58" t="n">
-        <v>97311</v>
+        <v>79876</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6641,21 +6641,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541962</v>
+        <v>542224</v>
       </c>
       <c r="R58" t="n">
-        <v>7063054</v>
+        <v>7063455</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6727,10 +6727,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122735524</v>
+        <v>122734876</v>
       </c>
       <c r="B59" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6739,25 +6739,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542224</v>
+        <v>542150</v>
       </c>
       <c r="R59" t="n">
-        <v>7063455</v>
+        <v>7063210</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6829,10 +6829,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122734876</v>
+        <v>122734495</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6841,25 +6841,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542150</v>
+        <v>542019</v>
       </c>
       <c r="R60" t="n">
-        <v>7063210</v>
+        <v>7063019</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122734495</v>
+        <v>122734184</v>
       </c>
       <c r="B61" t="n">
-        <v>79751</v>
+        <v>97311</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6947,21 +6947,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>542019</v>
+        <v>541962</v>
       </c>
       <c r="R61" t="n">
-        <v>7063019</v>
+        <v>7063054</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734998</v>
+        <v>122734614</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>79882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,43 +2463,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542180</v>
+        <v>542075</v>
       </c>
       <c r="R18" t="n">
-        <v>7063280</v>
+        <v>7063031</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2864,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122734614</v>
+        <v>122733626</v>
       </c>
       <c r="B22" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,25 +2871,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2899,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542075</v>
+        <v>541894</v>
       </c>
       <c r="R22" t="n">
-        <v>7063031</v>
+        <v>7063219</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2966,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122733626</v>
+        <v>122734998</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2982,34 +2977,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541894</v>
+        <v>542180</v>
       </c>
       <c r="R23" t="n">
-        <v>7063219</v>
+        <v>7063280</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734570</v>
+        <v>122734737</v>
       </c>
       <c r="B28" t="n">
-        <v>90955</v>
+        <v>56688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,34 +3506,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542057</v>
+        <v>542156</v>
       </c>
       <c r="R28" t="n">
-        <v>7063036</v>
+        <v>7063148</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3592,7 +3597,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122734737</v>
+        <v>122733611</v>
       </c>
       <c r="B29" t="n">
         <v>56688</v>
@@ -3637,10 +3642,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542156</v>
+        <v>541894</v>
       </c>
       <c r="R29" t="n">
-        <v>7063148</v>
+        <v>7063219</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3699,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733611</v>
+        <v>122734570</v>
       </c>
       <c r="B30" t="n">
-        <v>56688</v>
+        <v>90955</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,39 +3720,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541894</v>
+        <v>542057</v>
       </c>
       <c r="R30" t="n">
-        <v>7063219</v>
+        <v>7063036</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122735552</v>
+        <v>122740383</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5912,39 +5912,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542188</v>
+        <v>542117</v>
       </c>
       <c r="R51" t="n">
-        <v>7063472</v>
+        <v>7063503</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6003,10 +5998,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122740383</v>
+        <v>122735308</v>
       </c>
       <c r="B52" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6015,25 +6010,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6043,10 +6038,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542117</v>
+        <v>542199</v>
       </c>
       <c r="R52" t="n">
-        <v>7063503</v>
+        <v>7063368</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6105,10 +6100,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122735308</v>
+        <v>122734094</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6121,34 +6116,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542199</v>
+        <v>541918</v>
       </c>
       <c r="R53" t="n">
-        <v>7063368</v>
+        <v>7063050</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122734094</v>
+        <v>122735552</v>
       </c>
       <c r="B54" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6219,31 +6219,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541918</v>
+        <v>542188</v>
       </c>
       <c r="R54" t="n">
-        <v>7063050</v>
+        <v>7063472</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122733223</v>
+        <v>122734884</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,39 +2049,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541808</v>
+        <v>542151</v>
       </c>
       <c r="R14" t="n">
-        <v>7063277</v>
+        <v>7063216</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2140,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122734679</v>
+        <v>122734559</v>
       </c>
       <c r="B15" t="n">
-        <v>56680</v>
+        <v>90909</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,43 +2147,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542110</v>
+        <v>542051</v>
       </c>
       <c r="R15" t="n">
-        <v>7063060</v>
+        <v>7063037</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2247,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733563</v>
+        <v>122734661</v>
       </c>
       <c r="B16" t="n">
-        <v>88303</v>
+        <v>90909</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,25 +2249,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541868</v>
+        <v>542103</v>
       </c>
       <c r="R16" t="n">
-        <v>7063239</v>
+        <v>7063058</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2349,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122734167</v>
+        <v>122733821</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,34 +2355,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541962</v>
+        <v>541894</v>
       </c>
       <c r="R17" t="n">
-        <v>7063054</v>
+        <v>7063121</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2451,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734614</v>
+        <v>122734570</v>
       </c>
       <c r="B18" t="n">
-        <v>79882</v>
+        <v>90955</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2462,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542075</v>
+        <v>542057</v>
       </c>
       <c r="R18" t="n">
-        <v>7063031</v>
+        <v>7063036</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2553,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734480</v>
+        <v>122734232</v>
       </c>
       <c r="B19" t="n">
-        <v>90955</v>
+        <v>79883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,21 +2564,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2588,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542012</v>
+        <v>541952</v>
       </c>
       <c r="R19" t="n">
-        <v>7063013</v>
+        <v>7063000</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2655,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734884</v>
+        <v>122734625</v>
       </c>
       <c r="B20" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2667,25 +2662,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2695,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542151</v>
+        <v>542072</v>
       </c>
       <c r="R20" t="n">
-        <v>7063216</v>
+        <v>7063043</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2757,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122735193</v>
+        <v>122735552</v>
       </c>
       <c r="B21" t="n">
-        <v>90909</v>
+        <v>56688</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,34 +2768,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542209</v>
+        <v>542188</v>
       </c>
       <c r="R21" t="n">
-        <v>7063318</v>
+        <v>7063472</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122733626</v>
+        <v>122733573</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,38 +2871,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541894</v>
+        <v>541859</v>
       </c>
       <c r="R22" t="n">
-        <v>7063219</v>
+        <v>7063245</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2961,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122734998</v>
+        <v>122735193</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>90909</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,43 +2978,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542180</v>
+        <v>542209</v>
       </c>
       <c r="R23" t="n">
-        <v>7063280</v>
+        <v>7063318</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122733400</v>
+        <v>122740383</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>90909</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,42 +3080,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541821</v>
+        <v>542117</v>
       </c>
       <c r="R24" t="n">
-        <v>7063185</v>
+        <v>7063503</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3174,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122735514</v>
+        <v>122735254</v>
       </c>
       <c r="B25" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,25 +3182,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3214,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542225</v>
+        <v>542200</v>
       </c>
       <c r="R25" t="n">
-        <v>7063451</v>
+        <v>7063362</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3276,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122735437</v>
+        <v>122735491</v>
       </c>
       <c r="B26" t="n">
-        <v>79875</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3288,25 +3284,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3316,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542207</v>
+        <v>542222</v>
       </c>
       <c r="R26" t="n">
-        <v>7063420</v>
+        <v>7063450</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3490,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734737</v>
+        <v>122733563</v>
       </c>
       <c r="B28" t="n">
-        <v>56688</v>
+        <v>88303</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,43 +3498,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542156</v>
+        <v>541868</v>
       </c>
       <c r="R28" t="n">
-        <v>7063148</v>
+        <v>7063239</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3597,7 +3588,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733611</v>
+        <v>122734737</v>
       </c>
       <c r="B29" t="n">
         <v>56688</v>
@@ -3642,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541894</v>
+        <v>542156</v>
       </c>
       <c r="R29" t="n">
-        <v>7063219</v>
+        <v>7063148</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3704,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122734570</v>
+        <v>122733611</v>
       </c>
       <c r="B30" t="n">
-        <v>90955</v>
+        <v>56688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3720,34 +3711,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542057</v>
+        <v>541894</v>
       </c>
       <c r="R30" t="n">
-        <v>7063036</v>
+        <v>7063219</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3806,10 +3802,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122734932</v>
+        <v>122735514</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3818,20 +3814,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3846,10 +3842,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542178</v>
+        <v>542225</v>
       </c>
       <c r="R31" t="n">
-        <v>7063224</v>
+        <v>7063451</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3882,11 +3878,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3913,10 +3904,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122735414</v>
+        <v>122733746</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3925,31 +3916,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3958,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542209</v>
+        <v>541904</v>
       </c>
       <c r="R32" t="n">
-        <v>7063388</v>
+        <v>7063170</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3994,11 +3985,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4025,7 +4011,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734661</v>
+        <v>122733445</v>
       </c>
       <c r="B33" t="n">
         <v>90909</v>
@@ -4065,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542103</v>
+        <v>541842</v>
       </c>
       <c r="R33" t="n">
-        <v>7063058</v>
+        <v>7063190</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4127,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734625</v>
+        <v>122734495</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4139,25 +4125,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4167,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542072</v>
+        <v>542019</v>
       </c>
       <c r="R34" t="n">
-        <v>7063043</v>
+        <v>7063019</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4229,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122733598</v>
+        <v>122734433</v>
       </c>
       <c r="B35" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4241,43 +4227,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541891</v>
+        <v>542016</v>
       </c>
       <c r="R35" t="n">
-        <v>7063227</v>
+        <v>7063029</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4336,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122733445</v>
+        <v>122735414</v>
       </c>
       <c r="B36" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4348,38 +4329,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541842</v>
+        <v>542209</v>
       </c>
       <c r="R36" t="n">
-        <v>7063190</v>
+        <v>7063388</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4412,6 +4398,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,10 +4429,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122734559</v>
+        <v>122734191</v>
       </c>
       <c r="B37" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4450,25 +4441,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4478,10 +4469,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542051</v>
+        <v>541959</v>
       </c>
       <c r="R37" t="n">
-        <v>7063037</v>
+        <v>7063011</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4540,10 +4531,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122735491</v>
+        <v>122735524</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4552,25 +4543,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4580,10 +4571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542222</v>
+        <v>542224</v>
       </c>
       <c r="R38" t="n">
-        <v>7063450</v>
+        <v>7063455</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4642,10 +4633,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122733497</v>
+        <v>122734127</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4654,43 +4645,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541868</v>
+        <v>541949</v>
       </c>
       <c r="R39" t="n">
-        <v>7063207</v>
+        <v>7063047</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4749,10 +4735,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122733746</v>
+        <v>122734589</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4761,43 +4747,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541904</v>
+        <v>542061</v>
       </c>
       <c r="R40" t="n">
-        <v>7063170</v>
+        <v>7063040</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4856,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122735805</v>
+        <v>122734614</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79882</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4868,43 +4849,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542199</v>
+        <v>542075</v>
       </c>
       <c r="R41" t="n">
-        <v>7063483</v>
+        <v>7063031</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4937,11 +4913,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4968,10 +4939,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733946</v>
+        <v>122733412</v>
       </c>
       <c r="B42" t="n">
-        <v>74855</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4984,21 +4955,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5008,10 +4979,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541887</v>
+        <v>541827</v>
       </c>
       <c r="R42" t="n">
-        <v>7063133</v>
+        <v>7063182</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5070,10 +5041,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734524</v>
+        <v>122733654</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>79718</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5082,38 +5053,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542051</v>
+        <v>541896</v>
       </c>
       <c r="R43" t="n">
-        <v>7063037</v>
+        <v>7063207</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5154,6 +5128,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5172,10 +5147,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122733573</v>
+        <v>122734876</v>
       </c>
       <c r="B44" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5184,43 +5159,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541859</v>
+        <v>542150</v>
       </c>
       <c r="R44" t="n">
-        <v>7063245</v>
+        <v>7063210</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5279,10 +5249,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122735254</v>
+        <v>122734693</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5295,21 +5265,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5319,10 +5289,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542200</v>
+        <v>542111</v>
       </c>
       <c r="R45" t="n">
-        <v>7063362</v>
+        <v>7063060</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5381,10 +5351,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122733821</v>
+        <v>122734679</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5397,27 +5367,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5426,10 +5396,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541894</v>
+        <v>542110</v>
       </c>
       <c r="R46" t="n">
-        <v>7063121</v>
+        <v>7063060</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5488,10 +5458,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122734232</v>
+        <v>122734184</v>
       </c>
       <c r="B47" t="n">
-        <v>79883</v>
+        <v>97311</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5504,21 +5474,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5528,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541952</v>
+        <v>541962</v>
       </c>
       <c r="R47" t="n">
-        <v>7063000</v>
+        <v>7063054</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5590,10 +5560,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122734191</v>
+        <v>122735145</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5606,21 +5576,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5630,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541959</v>
+        <v>542201</v>
       </c>
       <c r="R48" t="n">
-        <v>7063011</v>
+        <v>7063315</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5692,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122734589</v>
+        <v>122735437</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>79875</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5704,25 +5674,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5732,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542061</v>
+        <v>542207</v>
       </c>
       <c r="R49" t="n">
-        <v>7063040</v>
+        <v>7063420</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5794,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122735145</v>
+        <v>122733598</v>
       </c>
       <c r="B50" t="n">
-        <v>90944</v>
+        <v>56688</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5806,38 +5776,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542201</v>
+        <v>541891</v>
       </c>
       <c r="R50" t="n">
-        <v>7063315</v>
+        <v>7063227</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5896,10 +5871,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122740383</v>
+        <v>122733859</v>
       </c>
       <c r="B51" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5908,25 +5883,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5936,10 +5911,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542117</v>
+        <v>541895</v>
       </c>
       <c r="R51" t="n">
-        <v>7063503</v>
+        <v>7063121</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5998,10 +5973,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122735308</v>
+        <v>122734709</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>91389</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,25 +5985,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6038,10 +6013,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542199</v>
+        <v>542116</v>
       </c>
       <c r="R52" t="n">
-        <v>7063368</v>
+        <v>7063065</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6100,10 +6075,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122734094</v>
+        <v>122734932</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6116,39 +6091,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541918</v>
+        <v>542178</v>
       </c>
       <c r="R53" t="n">
-        <v>7063050</v>
+        <v>7063224</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6181,6 +6151,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6207,10 +6182,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122735552</v>
+        <v>122734167</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6219,43 +6194,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542188</v>
+        <v>541962</v>
       </c>
       <c r="R54" t="n">
-        <v>7063472</v>
+        <v>7063054</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6314,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122734549</v>
+        <v>122734524</v>
       </c>
       <c r="B55" t="n">
-        <v>56078</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6330,29 +6300,24 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
@@ -6421,7 +6386,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122733412</v>
+        <v>122733626</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6461,10 +6426,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541827</v>
+        <v>541894</v>
       </c>
       <c r="R56" t="n">
-        <v>7063182</v>
+        <v>7063219</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6523,10 +6488,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734693</v>
+        <v>122734094</v>
       </c>
       <c r="B57" t="n">
-        <v>90944</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6539,34 +6504,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>542111</v>
+        <v>541918</v>
       </c>
       <c r="R57" t="n">
-        <v>7063060</v>
+        <v>7063050</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6625,10 +6595,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122735524</v>
+        <v>122735308</v>
       </c>
       <c r="B58" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6637,25 +6607,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6665,10 +6635,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542224</v>
+        <v>542199</v>
       </c>
       <c r="R58" t="n">
-        <v>7063455</v>
+        <v>7063368</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6727,10 +6697,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122734876</v>
+        <v>122735805</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6743,34 +6713,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542150</v>
+        <v>542199</v>
       </c>
       <c r="R59" t="n">
-        <v>7063210</v>
+        <v>7063483</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6803,6 +6778,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6829,10 +6809,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122734495</v>
+        <v>122733497</v>
       </c>
       <c r="B60" t="n">
-        <v>79751</v>
+        <v>56688</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6845,34 +6825,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542019</v>
+        <v>541868</v>
       </c>
       <c r="R60" t="n">
-        <v>7063019</v>
+        <v>7063207</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6931,10 +6916,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122734184</v>
+        <v>122733223</v>
       </c>
       <c r="B61" t="n">
-        <v>97311</v>
+        <v>56688</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6947,34 +6932,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541962</v>
+        <v>541808</v>
       </c>
       <c r="R61" t="n">
-        <v>7063054</v>
+        <v>7063277</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7033,10 +7023,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122733859</v>
+        <v>122734549</v>
       </c>
       <c r="B62" t="n">
-        <v>90944</v>
+        <v>56078</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7049,34 +7039,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541895</v>
+        <v>542051</v>
       </c>
       <c r="R62" t="n">
-        <v>7063121</v>
+        <v>7063037</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7135,10 +7130,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122734709</v>
+        <v>122733946</v>
       </c>
       <c r="B63" t="n">
-        <v>91389</v>
+        <v>74855</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7147,25 +7142,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7175,10 +7170,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542116</v>
+        <v>541887</v>
       </c>
       <c r="R63" t="n">
-        <v>7063065</v>
+        <v>7063133</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7237,10 +7232,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122733654</v>
+        <v>122733400</v>
       </c>
       <c r="B64" t="n">
-        <v>79718</v>
+        <v>98357</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7253,37 +7248,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>389</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541896</v>
+        <v>541821</v>
       </c>
       <c r="R64" t="n">
-        <v>7063207</v>
+        <v>7063185</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7324,7 +7320,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7343,10 +7338,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122734127</v>
+        <v>122734998</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7359,34 +7354,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541949</v>
+        <v>542180</v>
       </c>
       <c r="R65" t="n">
-        <v>7063047</v>
+        <v>7063280</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7445,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122734433</v>
+        <v>122734480</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>90955</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7457,25 +7457,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7485,10 +7485,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>542016</v>
+        <v>542012</v>
       </c>
       <c r="R66" t="n">
-        <v>7063029</v>
+        <v>7063013</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -3486,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122733563</v>
+        <v>122734737</v>
       </c>
       <c r="B28" t="n">
-        <v>88303</v>
+        <v>56688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3498,38 +3498,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541868</v>
+        <v>542156</v>
       </c>
       <c r="R28" t="n">
-        <v>7063239</v>
+        <v>7063148</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3588,7 +3593,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122734737</v>
+        <v>122733611</v>
       </c>
       <c r="B29" t="n">
         <v>56688</v>
@@ -3633,10 +3638,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542156</v>
+        <v>541894</v>
       </c>
       <c r="R29" t="n">
-        <v>7063148</v>
+        <v>7063219</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3695,10 +3700,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733611</v>
+        <v>122733563</v>
       </c>
       <c r="B30" t="n">
-        <v>56688</v>
+        <v>88303</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,43 +3712,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541894</v>
+        <v>541868</v>
       </c>
       <c r="R30" t="n">
-        <v>7063219</v>
+        <v>7063239</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -5764,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122733598</v>
+        <v>122733859</v>
       </c>
       <c r="B50" t="n">
-        <v>56688</v>
+        <v>90944</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5776,43 +5776,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541891</v>
+        <v>541895</v>
       </c>
       <c r="R50" t="n">
-        <v>7063227</v>
+        <v>7063121</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5871,10 +5866,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122733859</v>
+        <v>122734167</v>
       </c>
       <c r="B51" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5887,21 +5882,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5911,10 +5906,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541895</v>
+        <v>541962</v>
       </c>
       <c r="R51" t="n">
-        <v>7063121</v>
+        <v>7063054</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6182,10 +6177,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122734167</v>
+        <v>122733598</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,38 +6189,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541962</v>
+        <v>541891</v>
       </c>
       <c r="R54" t="n">
-        <v>7063054</v>
+        <v>7063227</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2036,7 +2036,7 @@
         <v>122734884</v>
       </c>
       <c r="B14" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122734559</v>
+        <v>122735524</v>
       </c>
       <c r="B15" t="n">
-        <v>90909</v>
+        <v>79876</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542051</v>
+        <v>542224</v>
       </c>
       <c r="R15" t="n">
-        <v>7063037</v>
+        <v>7063455</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122734661</v>
+        <v>122734167</v>
       </c>
       <c r="B16" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,25 +2249,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542103</v>
+        <v>541962</v>
       </c>
       <c r="R16" t="n">
-        <v>7063058</v>
+        <v>7063054</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733821</v>
+        <v>122734184</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,43 +2351,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541894</v>
+        <v>541962</v>
       </c>
       <c r="R17" t="n">
-        <v>7063121</v>
+        <v>7063054</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2446,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734570</v>
+        <v>122733623</v>
       </c>
       <c r="B18" t="n">
-        <v>90955</v>
+        <v>56688</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2462,34 +2457,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542057</v>
+        <v>541894</v>
       </c>
       <c r="R18" t="n">
-        <v>7063036</v>
+        <v>7063219</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2548,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734232</v>
+        <v>122734737</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,34 +2564,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541952</v>
+        <v>542156</v>
       </c>
       <c r="R19" t="n">
-        <v>7063000</v>
+        <v>7063148</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2650,10 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734625</v>
+        <v>122734549</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>56078</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,34 +2671,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542072</v>
+        <v>542051</v>
       </c>
       <c r="R20" t="n">
-        <v>7063043</v>
+        <v>7063037</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2752,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122735552</v>
+        <v>122735193</v>
       </c>
       <c r="B21" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,39 +2778,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542188</v>
+        <v>542209</v>
       </c>
       <c r="R21" t="n">
-        <v>7063472</v>
+        <v>7063318</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2859,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122733573</v>
+        <v>122733821</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,31 +2876,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2904,10 +2909,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541859</v>
+        <v>541894</v>
       </c>
       <c r="R22" t="n">
-        <v>7063245</v>
+        <v>7063121</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2966,10 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122735193</v>
+        <v>122735308</v>
       </c>
       <c r="B23" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,25 +2983,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3006,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542209</v>
+        <v>542199</v>
       </c>
       <c r="R23" t="n">
-        <v>7063318</v>
+        <v>7063368</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3068,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122740383</v>
+        <v>122733626</v>
       </c>
       <c r="B24" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,25 +3085,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542117</v>
+        <v>541894</v>
       </c>
       <c r="R24" t="n">
-        <v>7063503</v>
+        <v>7063219</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3170,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122735254</v>
+        <v>122734661</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3182,25 +3187,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3210,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542200</v>
+        <v>542103</v>
       </c>
       <c r="R25" t="n">
-        <v>7063362</v>
+        <v>7063058</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3272,7 +3277,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122735491</v>
+        <v>122734433</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3312,10 +3317,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542222</v>
+        <v>542016</v>
       </c>
       <c r="R26" t="n">
-        <v>7063450</v>
+        <v>7063029</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3374,10 +3379,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122733368</v>
+        <v>122733412</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,39 +3395,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541796</v>
+        <v>541827</v>
       </c>
       <c r="R27" t="n">
-        <v>7063200</v>
+        <v>7063182</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3455,11 +3455,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,7 +3481,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734737</v>
+        <v>122733223</v>
       </c>
       <c r="B28" t="n">
         <v>56688</v>
@@ -3531,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542156</v>
+        <v>541808</v>
       </c>
       <c r="R28" t="n">
-        <v>7063148</v>
+        <v>7063277</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3593,7 +3588,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733611</v>
+        <v>122733497</v>
       </c>
       <c r="B29" t="n">
         <v>56688</v>
@@ -3638,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541894</v>
+        <v>541868</v>
       </c>
       <c r="R29" t="n">
-        <v>7063219</v>
+        <v>7063207</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3700,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733563</v>
+        <v>122735145</v>
       </c>
       <c r="B30" t="n">
-        <v>88303</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3716,21 +3711,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541868</v>
+        <v>542201</v>
       </c>
       <c r="R30" t="n">
-        <v>7063239</v>
+        <v>7063315</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3802,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122735514</v>
+        <v>122733946</v>
       </c>
       <c r="B31" t="n">
-        <v>79882</v>
+        <v>74855</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3814,25 +3809,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3842,10 +3837,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542225</v>
+        <v>541887</v>
       </c>
       <c r="R31" t="n">
-        <v>7063451</v>
+        <v>7063133</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3904,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122733746</v>
+        <v>122734709</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>91397</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3916,43 +3911,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541904</v>
+        <v>542116</v>
       </c>
       <c r="R32" t="n">
-        <v>7063170</v>
+        <v>7063065</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,10 +4001,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122733445</v>
+        <v>122733563</v>
       </c>
       <c r="B33" t="n">
-        <v>90909</v>
+        <v>88303</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4023,25 +4013,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4051,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541842</v>
+        <v>541868</v>
       </c>
       <c r="R33" t="n">
-        <v>7063190</v>
+        <v>7063239</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,10 +4103,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734495</v>
+        <v>122735254</v>
       </c>
       <c r="B34" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4125,25 +4115,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542019</v>
+        <v>542200</v>
       </c>
       <c r="R34" t="n">
-        <v>7063019</v>
+        <v>7063362</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4215,10 +4205,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122734433</v>
+        <v>122733573</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4227,38 +4217,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542016</v>
+        <v>541859</v>
       </c>
       <c r="R35" t="n">
-        <v>7063029</v>
+        <v>7063245</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4317,10 +4312,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122735414</v>
+        <v>122733598</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4329,31 +4324,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542209</v>
+        <v>541891</v>
       </c>
       <c r="R36" t="n">
-        <v>7063388</v>
+        <v>7063227</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4398,11 +4393,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4429,10 +4419,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122734191</v>
+        <v>122735437</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>79875</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4441,25 +4431,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4469,10 +4459,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541959</v>
+        <v>542207</v>
       </c>
       <c r="R37" t="n">
-        <v>7063011</v>
+        <v>7063420</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4531,10 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122735524</v>
+        <v>122733746</v>
       </c>
       <c r="B38" t="n">
-        <v>79876</v>
+        <v>56688</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4547,34 +4537,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542224</v>
+        <v>541904</v>
       </c>
       <c r="R38" t="n">
-        <v>7063455</v>
+        <v>7063170</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4633,10 +4628,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122734127</v>
+        <v>122735514</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4645,25 +4640,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4673,10 +4668,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541949</v>
+        <v>542225</v>
       </c>
       <c r="R39" t="n">
-        <v>7063047</v>
+        <v>7063451</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4735,10 +4730,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734589</v>
+        <v>122734614</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,25 +4742,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4775,10 +4770,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542061</v>
+        <v>542075</v>
       </c>
       <c r="R40" t="n">
-        <v>7063040</v>
+        <v>7063031</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4837,10 +4832,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734614</v>
+        <v>122734998</v>
       </c>
       <c r="B41" t="n">
-        <v>79882</v>
+        <v>57631</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4849,38 +4844,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542075</v>
+        <v>542180</v>
       </c>
       <c r="R41" t="n">
-        <v>7063031</v>
+        <v>7063280</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4939,10 +4939,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733412</v>
+        <v>122733368</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4955,34 +4955,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541827</v>
+        <v>541796</v>
       </c>
       <c r="R42" t="n">
-        <v>7063182</v>
+        <v>7063200</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5015,6 +5020,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,10 +5051,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122733654</v>
+        <v>122734876</v>
       </c>
       <c r="B43" t="n">
-        <v>79718</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5053,41 +5063,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541896</v>
+        <v>542150</v>
       </c>
       <c r="R43" t="n">
-        <v>7063207</v>
+        <v>7063210</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5128,7 +5135,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5147,7 +5153,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122734876</v>
+        <v>122734127</v>
       </c>
       <c r="B44" t="n">
         <v>79847</v>
@@ -5187,10 +5193,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542150</v>
+        <v>541949</v>
       </c>
       <c r="R44" t="n">
-        <v>7063210</v>
+        <v>7063047</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5249,10 +5255,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122734693</v>
+        <v>122733859</v>
       </c>
       <c r="B45" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5289,10 +5295,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542111</v>
+        <v>541895</v>
       </c>
       <c r="R45" t="n">
-        <v>7063060</v>
+        <v>7063121</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5351,10 +5357,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734679</v>
+        <v>122733654</v>
       </c>
       <c r="B46" t="n">
-        <v>56680</v>
+        <v>79718</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5363,43 +5369,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>389</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542110</v>
+        <v>541896</v>
       </c>
       <c r="R46" t="n">
-        <v>7063060</v>
+        <v>7063207</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5440,6 +5444,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5458,10 +5463,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122734184</v>
+        <v>122734232</v>
       </c>
       <c r="B47" t="n">
-        <v>97311</v>
+        <v>79883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5474,21 +5479,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5498,10 +5503,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541962</v>
+        <v>541952</v>
       </c>
       <c r="R47" t="n">
-        <v>7063054</v>
+        <v>7063000</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5560,10 +5565,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122735145</v>
+        <v>122735414</v>
       </c>
       <c r="B48" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5576,34 +5581,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542201</v>
+        <v>542209</v>
       </c>
       <c r="R48" t="n">
-        <v>7063315</v>
+        <v>7063388</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5636,6 +5646,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5662,10 +5677,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122735437</v>
+        <v>122734495</v>
       </c>
       <c r="B49" t="n">
-        <v>79875</v>
+        <v>79751</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5678,21 +5693,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5702,10 +5717,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542207</v>
+        <v>542019</v>
       </c>
       <c r="R49" t="n">
-        <v>7063420</v>
+        <v>7063019</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5764,10 +5779,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122733859</v>
+        <v>122734524</v>
       </c>
       <c r="B50" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,21 +5795,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5819,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541895</v>
+        <v>542051</v>
       </c>
       <c r="R50" t="n">
-        <v>7063121</v>
+        <v>7063037</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5866,10 +5881,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122734167</v>
+        <v>122734094</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5882,34 +5897,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541962</v>
+        <v>541918</v>
       </c>
       <c r="R51" t="n">
-        <v>7063054</v>
+        <v>7063050</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5968,10 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734709</v>
+        <v>122734191</v>
       </c>
       <c r="B52" t="n">
-        <v>91389</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5980,25 +6000,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6008,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542116</v>
+        <v>541959</v>
       </c>
       <c r="R52" t="n">
-        <v>7063065</v>
+        <v>7063011</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6070,10 +6090,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122734932</v>
+        <v>122734589</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6086,21 +6106,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6110,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542178</v>
+        <v>542061</v>
       </c>
       <c r="R53" t="n">
-        <v>7063224</v>
+        <v>7063040</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6146,11 +6166,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6177,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122733598</v>
+        <v>122735805</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6189,31 +6204,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6222,10 +6237,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541891</v>
+        <v>542199</v>
       </c>
       <c r="R54" t="n">
-        <v>7063227</v>
+        <v>7063483</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6258,6 +6273,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6284,10 +6304,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122734524</v>
+        <v>122734693</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,21 +6320,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6324,10 +6344,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542051</v>
+        <v>542111</v>
       </c>
       <c r="R55" t="n">
-        <v>7063037</v>
+        <v>7063060</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6386,10 +6406,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122733626</v>
+        <v>122733445</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6398,25 +6418,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6426,10 +6446,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541894</v>
+        <v>541842</v>
       </c>
       <c r="R56" t="n">
-        <v>7063219</v>
+        <v>7063190</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6488,10 +6508,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734094</v>
+        <v>122734932</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6504,39 +6524,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541918</v>
+        <v>542178</v>
       </c>
       <c r="R57" t="n">
-        <v>7063050</v>
+        <v>7063224</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6569,6 +6584,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6595,10 +6615,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122735308</v>
+        <v>122734570</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6607,25 +6627,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6635,10 +6655,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542199</v>
+        <v>542057</v>
       </c>
       <c r="R58" t="n">
-        <v>7063368</v>
+        <v>7063036</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6697,10 +6717,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122735805</v>
+        <v>122735552</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6709,31 +6729,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6742,10 +6762,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542199</v>
+        <v>542188</v>
       </c>
       <c r="R59" t="n">
-        <v>7063483</v>
+        <v>7063472</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6778,11 +6798,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6809,10 +6824,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122733497</v>
+        <v>122734679</v>
       </c>
       <c r="B60" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6821,25 +6836,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6854,10 +6869,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541868</v>
+        <v>542110</v>
       </c>
       <c r="R60" t="n">
-        <v>7063207</v>
+        <v>7063060</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6916,10 +6931,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122733223</v>
+        <v>122733400</v>
       </c>
       <c r="B61" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6928,31 +6943,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6961,10 +6975,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541808</v>
+        <v>541821</v>
       </c>
       <c r="R61" t="n">
-        <v>7063277</v>
+        <v>7063185</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7023,10 +7037,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122734549</v>
+        <v>122734559</v>
       </c>
       <c r="B62" t="n">
-        <v>56078</v>
+        <v>90917</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7035,33 +7049,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
@@ -7130,10 +7139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122733946</v>
+        <v>122734480</v>
       </c>
       <c r="B63" t="n">
-        <v>74855</v>
+        <v>90963</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7142,25 +7151,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>1205</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7170,10 +7179,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541887</v>
+        <v>542012</v>
       </c>
       <c r="R63" t="n">
-        <v>7063133</v>
+        <v>7063013</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7232,10 +7241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122733400</v>
+        <v>122735491</v>
       </c>
       <c r="B64" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7244,42 +7253,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541821</v>
+        <v>542222</v>
       </c>
       <c r="R64" t="n">
-        <v>7063185</v>
+        <v>7063450</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7338,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122734998</v>
+        <v>122740383</v>
       </c>
       <c r="B65" t="n">
-        <v>57631</v>
+        <v>90917</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7350,43 +7355,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542180</v>
+        <v>542117</v>
       </c>
       <c r="R65" t="n">
-        <v>7063280</v>
+        <v>7063503</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7445,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122734480</v>
+        <v>122734625</v>
       </c>
       <c r="B66" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7457,25 +7457,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7485,10 +7485,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>542012</v>
+        <v>542072</v>
       </c>
       <c r="R66" t="n">
-        <v>7063013</v>
+        <v>7063043</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122734709</v>
+        <v>122733563</v>
       </c>
       <c r="B32" t="n">
-        <v>91397</v>
+        <v>88303</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3911,25 +3911,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542116</v>
+        <v>541868</v>
       </c>
       <c r="R32" t="n">
-        <v>7063065</v>
+        <v>7063239</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122733563</v>
+        <v>122734709</v>
       </c>
       <c r="B33" t="n">
-        <v>88303</v>
+        <v>91397</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4013,25 +4013,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541868</v>
+        <v>542116</v>
       </c>
       <c r="R33" t="n">
-        <v>7063239</v>
+        <v>7063065</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122733654</v>
+        <v>122734232</v>
       </c>
       <c r="B46" t="n">
-        <v>79718</v>
+        <v>79883</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5369,41 +5369,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>389</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541896</v>
+        <v>541952</v>
       </c>
       <c r="R46" t="n">
-        <v>7063207</v>
+        <v>7063000</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5444,7 +5441,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5463,10 +5459,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122734232</v>
+        <v>122733654</v>
       </c>
       <c r="B47" t="n">
-        <v>79883</v>
+        <v>79718</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5475,38 +5471,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>389</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541952</v>
+        <v>541896</v>
       </c>
       <c r="R47" t="n">
-        <v>7063000</v>
+        <v>7063207</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5547,6 +5546,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734191</v>
+        <v>122734693</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541959</v>
+        <v>542111</v>
       </c>
       <c r="R52" t="n">
-        <v>7063011</v>
+        <v>7063060</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122734589</v>
+        <v>122734191</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542061</v>
+        <v>541959</v>
       </c>
       <c r="R53" t="n">
-        <v>7063040</v>
+        <v>7063011</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122735805</v>
+        <v>122734589</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6208,39 +6208,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542199</v>
+        <v>542061</v>
       </c>
       <c r="R54" t="n">
-        <v>7063483</v>
+        <v>7063040</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6273,11 +6268,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6304,10 +6294,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122734693</v>
+        <v>122735805</v>
       </c>
       <c r="B55" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6320,34 +6310,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542111</v>
+        <v>542199</v>
       </c>
       <c r="R55" t="n">
-        <v>7063060</v>
+        <v>7063483</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6380,6 +6375,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122734884</v>
+        <v>122733746</v>
       </c>
       <c r="B14" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,34 +2049,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542151</v>
+        <v>541904</v>
       </c>
       <c r="R14" t="n">
-        <v>7063216</v>
+        <v>7063170</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2135,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122735524</v>
+        <v>122735193</v>
       </c>
       <c r="B15" t="n">
-        <v>79876</v>
+        <v>90917</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542224</v>
+        <v>542209</v>
       </c>
       <c r="R15" t="n">
-        <v>7063455</v>
+        <v>7063318</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2237,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122734167</v>
+        <v>122733598</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,38 +2254,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541962</v>
+        <v>541891</v>
       </c>
       <c r="R16" t="n">
-        <v>7063054</v>
+        <v>7063227</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2339,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122734184</v>
+        <v>122733611</v>
       </c>
       <c r="B17" t="n">
-        <v>97319</v>
+        <v>56688</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,34 +2365,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541962</v>
+        <v>541894</v>
       </c>
       <c r="R17" t="n">
-        <v>7063054</v>
+        <v>7063219</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2441,10 +2456,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122733623</v>
+        <v>122735805</v>
       </c>
       <c r="B18" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,31 +2468,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2486,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541894</v>
+        <v>542199</v>
       </c>
       <c r="R18" t="n">
-        <v>7063219</v>
+        <v>7063483</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2522,6 +2537,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734737</v>
+        <v>122734876</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,43 +2580,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542156</v>
+        <v>542150</v>
       </c>
       <c r="R19" t="n">
-        <v>7063148</v>
+        <v>7063210</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2655,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734549</v>
+        <v>122735308</v>
       </c>
       <c r="B20" t="n">
-        <v>56078</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,39 +2686,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542051</v>
+        <v>542199</v>
       </c>
       <c r="R20" t="n">
-        <v>7063037</v>
+        <v>7063368</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2762,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122735193</v>
+        <v>122734589</v>
       </c>
       <c r="B21" t="n">
-        <v>90917</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,25 +2784,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2802,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542209</v>
+        <v>542061</v>
       </c>
       <c r="R21" t="n">
-        <v>7063318</v>
+        <v>7063040</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2864,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122733821</v>
+        <v>122740383</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>90917</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,43 +2886,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541894</v>
+        <v>542117</v>
       </c>
       <c r="R22" t="n">
-        <v>7063121</v>
+        <v>7063503</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2971,10 +2976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122735308</v>
+        <v>122734661</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2983,25 +2988,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3011,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542199</v>
+        <v>542103</v>
       </c>
       <c r="R23" t="n">
-        <v>7063368</v>
+        <v>7063058</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3073,10 +3078,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122733626</v>
+        <v>122735552</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,38 +3090,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541894</v>
+        <v>542188</v>
       </c>
       <c r="R24" t="n">
-        <v>7063219</v>
+        <v>7063472</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3175,10 +3185,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122734661</v>
+        <v>122733223</v>
       </c>
       <c r="B25" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,34 +3201,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542103</v>
+        <v>541808</v>
       </c>
       <c r="R25" t="n">
-        <v>7063058</v>
+        <v>7063277</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3277,10 +3292,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122734433</v>
+        <v>122734549</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>56078</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,34 +3308,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542016</v>
+        <v>542051</v>
       </c>
       <c r="R26" t="n">
-        <v>7063029</v>
+        <v>7063037</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3379,7 +3399,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122733412</v>
+        <v>122735491</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3419,10 +3439,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541827</v>
+        <v>542222</v>
       </c>
       <c r="R27" t="n">
-        <v>7063182</v>
+        <v>7063450</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3481,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122733223</v>
+        <v>122734625</v>
       </c>
       <c r="B28" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3493,43 +3513,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541808</v>
+        <v>542072</v>
       </c>
       <c r="R28" t="n">
-        <v>7063277</v>
+        <v>7063043</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3588,7 +3603,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733497</v>
+        <v>122733573</v>
       </c>
       <c r="B29" t="n">
         <v>56688</v>
@@ -3633,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541868</v>
+        <v>541859</v>
       </c>
       <c r="R29" t="n">
-        <v>7063207</v>
+        <v>7063245</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3695,7 +3710,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122735145</v>
+        <v>122733859</v>
       </c>
       <c r="B30" t="n">
         <v>90952</v>
@@ -3735,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542201</v>
+        <v>541895</v>
       </c>
       <c r="R30" t="n">
-        <v>7063315</v>
+        <v>7063121</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3797,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122733946</v>
+        <v>122734524</v>
       </c>
       <c r="B31" t="n">
-        <v>74855</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3813,21 +3828,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3837,10 +3852,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541887</v>
+        <v>542051</v>
       </c>
       <c r="R31" t="n">
-        <v>7063133</v>
+        <v>7063037</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3899,10 +3914,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122733563</v>
+        <v>122733400</v>
       </c>
       <c r="B32" t="n">
-        <v>88303</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3911,38 +3926,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541868</v>
+        <v>541821</v>
       </c>
       <c r="R32" t="n">
-        <v>7063239</v>
+        <v>7063185</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4001,10 +4020,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734709</v>
+        <v>122734737</v>
       </c>
       <c r="B33" t="n">
-        <v>91397</v>
+        <v>56688</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4013,38 +4032,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542116</v>
+        <v>542156</v>
       </c>
       <c r="R33" t="n">
-        <v>7063065</v>
+        <v>7063148</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4103,10 +4127,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122735254</v>
+        <v>122734679</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4119,34 +4143,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542200</v>
+        <v>542110</v>
       </c>
       <c r="R34" t="n">
-        <v>7063362</v>
+        <v>7063060</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4205,10 +4234,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122733573</v>
+        <v>122734570</v>
       </c>
       <c r="B35" t="n">
-        <v>56688</v>
+        <v>90963</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4221,39 +4250,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541859</v>
+        <v>542057</v>
       </c>
       <c r="R35" t="n">
-        <v>7063245</v>
+        <v>7063036</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4312,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122733598</v>
+        <v>122734559</v>
       </c>
       <c r="B36" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4328,39 +4352,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541891</v>
+        <v>542051</v>
       </c>
       <c r="R36" t="n">
-        <v>7063227</v>
+        <v>7063037</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4419,10 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122735437</v>
+        <v>122734932</v>
       </c>
       <c r="B37" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4431,25 +4450,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4459,10 +4478,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542207</v>
+        <v>542178</v>
       </c>
       <c r="R37" t="n">
-        <v>7063420</v>
+        <v>7063224</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4495,6 +4514,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4521,10 +4545,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122733746</v>
+        <v>122733412</v>
       </c>
       <c r="B38" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4533,43 +4557,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541904</v>
+        <v>541827</v>
       </c>
       <c r="R38" t="n">
-        <v>7063170</v>
+        <v>7063182</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4628,10 +4647,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122735514</v>
+        <v>122733626</v>
       </c>
       <c r="B39" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4640,25 +4659,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4668,10 +4687,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542225</v>
+        <v>541894</v>
       </c>
       <c r="R39" t="n">
-        <v>7063451</v>
+        <v>7063219</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4730,10 +4749,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734614</v>
+        <v>122734232</v>
       </c>
       <c r="B40" t="n">
-        <v>79882</v>
+        <v>79883</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4746,21 +4765,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4770,10 +4789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542075</v>
+        <v>541952</v>
       </c>
       <c r="R40" t="n">
-        <v>7063031</v>
+        <v>7063000</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4832,10 +4851,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734998</v>
+        <v>122734693</v>
       </c>
       <c r="B41" t="n">
-        <v>57631</v>
+        <v>90952</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4848,39 +4867,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542180</v>
+        <v>542111</v>
       </c>
       <c r="R41" t="n">
-        <v>7063280</v>
+        <v>7063060</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4939,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733368</v>
+        <v>122734167</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4955,39 +4969,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541796</v>
+        <v>541962</v>
       </c>
       <c r="R42" t="n">
-        <v>7063200</v>
+        <v>7063054</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5020,11 +5029,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5051,10 +5055,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734876</v>
+        <v>122733821</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5067,34 +5071,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542150</v>
+        <v>541894</v>
       </c>
       <c r="R43" t="n">
-        <v>7063210</v>
+        <v>7063121</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5153,10 +5162,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122734127</v>
+        <v>122735524</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5165,25 +5174,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5193,10 +5202,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541949</v>
+        <v>542224</v>
       </c>
       <c r="R44" t="n">
-        <v>7063047</v>
+        <v>7063455</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5255,10 +5264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122733859</v>
+        <v>122735254</v>
       </c>
       <c r="B45" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5271,21 +5280,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5295,10 +5304,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541895</v>
+        <v>542200</v>
       </c>
       <c r="R45" t="n">
-        <v>7063121</v>
+        <v>7063362</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5357,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734232</v>
+        <v>122734998</v>
       </c>
       <c r="B46" t="n">
-        <v>79883</v>
+        <v>57631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5369,38 +5378,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541952</v>
+        <v>542180</v>
       </c>
       <c r="R46" t="n">
-        <v>7063000</v>
+        <v>7063280</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5459,10 +5473,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122733654</v>
+        <v>122734094</v>
       </c>
       <c r="B47" t="n">
-        <v>79718</v>
+        <v>57494</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5471,41 +5485,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>389</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541896</v>
+        <v>541918</v>
       </c>
       <c r="R47" t="n">
-        <v>7063207</v>
+        <v>7063050</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5546,7 +5562,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5565,7 +5580,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122735414</v>
+        <v>122733348</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5601,7 +5616,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5610,10 +5625,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542209</v>
+        <v>541796</v>
       </c>
       <c r="R48" t="n">
-        <v>7063388</v>
+        <v>7063200</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5650,7 +5665,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5677,10 +5692,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122734495</v>
+        <v>122733497</v>
       </c>
       <c r="B49" t="n">
-        <v>79751</v>
+        <v>56688</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5693,34 +5708,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542019</v>
+        <v>541868</v>
       </c>
       <c r="R49" t="n">
-        <v>7063019</v>
+        <v>7063207</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5779,10 +5799,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122734524</v>
+        <v>122734184</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>97319</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5791,25 +5811,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5819,10 +5839,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542051</v>
+        <v>541962</v>
       </c>
       <c r="R50" t="n">
-        <v>7063037</v>
+        <v>7063054</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5881,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122734094</v>
+        <v>122734480</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>90963</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5893,43 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541918</v>
+        <v>542012</v>
       </c>
       <c r="R51" t="n">
-        <v>7063050</v>
+        <v>7063013</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5988,10 +6003,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734693</v>
+        <v>122734884</v>
       </c>
       <c r="B52" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6000,25 +6015,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6028,10 +6043,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542111</v>
+        <v>542151</v>
       </c>
       <c r="R52" t="n">
-        <v>7063060</v>
+        <v>7063216</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6090,10 +6105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122734191</v>
+        <v>122735437</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>79875</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6102,25 +6117,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6130,10 +6145,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541959</v>
+        <v>542207</v>
       </c>
       <c r="R53" t="n">
-        <v>7063011</v>
+        <v>7063420</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6192,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122734589</v>
+        <v>122733563</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>88303</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6208,21 +6223,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6232,10 +6247,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542061</v>
+        <v>541868</v>
       </c>
       <c r="R54" t="n">
-        <v>7063040</v>
+        <v>7063239</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6294,10 +6309,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122735805</v>
+        <v>122733946</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>74855</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6310,39 +6325,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542199</v>
+        <v>541887</v>
       </c>
       <c r="R55" t="n">
-        <v>7063483</v>
+        <v>7063133</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6375,11 +6385,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6406,10 +6411,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122733445</v>
+        <v>122734495</v>
       </c>
       <c r="B56" t="n">
-        <v>90917</v>
+        <v>79751</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6422,21 +6427,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541842</v>
+        <v>542019</v>
       </c>
       <c r="R56" t="n">
-        <v>7063190</v>
+        <v>7063019</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6508,10 +6513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734932</v>
+        <v>122734127</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6524,21 +6529,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6548,10 +6553,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>542178</v>
+        <v>541949</v>
       </c>
       <c r="R57" t="n">
-        <v>7063224</v>
+        <v>7063047</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6584,11 +6589,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6615,10 +6615,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122734570</v>
+        <v>122735514</v>
       </c>
       <c r="B58" t="n">
-        <v>90963</v>
+        <v>79882</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6631,21 +6631,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542057</v>
+        <v>542225</v>
       </c>
       <c r="R58" t="n">
-        <v>7063036</v>
+        <v>7063451</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122735552</v>
+        <v>122733445</v>
       </c>
       <c r="B59" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6733,39 +6733,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542188</v>
+        <v>541842</v>
       </c>
       <c r="R59" t="n">
-        <v>7063472</v>
+        <v>7063190</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6824,10 +6819,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122734679</v>
+        <v>122734614</v>
       </c>
       <c r="B60" t="n">
-        <v>56680</v>
+        <v>79882</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6836,43 +6831,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542110</v>
+        <v>542075</v>
       </c>
       <c r="R60" t="n">
-        <v>7063060</v>
+        <v>7063031</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6931,10 +6921,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122733400</v>
+        <v>122735414</v>
       </c>
       <c r="B61" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6943,30 +6933,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6975,10 +6966,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541821</v>
+        <v>542209</v>
       </c>
       <c r="R61" t="n">
-        <v>7063185</v>
+        <v>7063388</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7011,6 +7002,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7037,10 +7033,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122734559</v>
+        <v>122733654</v>
       </c>
       <c r="B62" t="n">
-        <v>90917</v>
+        <v>79718</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7049,38 +7045,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>389</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>542051</v>
+        <v>541896</v>
       </c>
       <c r="R62" t="n">
-        <v>7063037</v>
+        <v>7063207</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7121,6 +7120,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122734480</v>
+        <v>122734709</v>
       </c>
       <c r="B63" t="n">
-        <v>90963</v>
+        <v>91397</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7151,25 +7151,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542012</v>
+        <v>542116</v>
       </c>
       <c r="R63" t="n">
-        <v>7063013</v>
+        <v>7063065</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122735491</v>
+        <v>122735145</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7257,21 +7257,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542222</v>
+        <v>542201</v>
       </c>
       <c r="R64" t="n">
-        <v>7063450</v>
+        <v>7063315</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122740383</v>
+        <v>122734433</v>
       </c>
       <c r="B65" t="n">
-        <v>90917</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7355,25 +7355,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542117</v>
+        <v>542016</v>
       </c>
       <c r="R65" t="n">
-        <v>7063503</v>
+        <v>7063029</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122734625</v>
+        <v>122734191</v>
       </c>
       <c r="B66" t="n">
         <v>79847</v>
@@ -7485,10 +7485,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>542072</v>
+        <v>541959</v>
       </c>
       <c r="R66" t="n">
-        <v>7063043</v>
+        <v>7063011</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -4020,10 +4020,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734737</v>
+        <v>122734570</v>
       </c>
       <c r="B33" t="n">
-        <v>56688</v>
+        <v>90963</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,39 +4036,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542156</v>
+        <v>542057</v>
       </c>
       <c r="R33" t="n">
-        <v>7063148</v>
+        <v>7063036</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4127,10 +4122,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734679</v>
+        <v>122734737</v>
       </c>
       <c r="B34" t="n">
-        <v>56680</v>
+        <v>56688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4139,25 +4134,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4172,10 +4167,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542110</v>
+        <v>542156</v>
       </c>
       <c r="R34" t="n">
-        <v>7063060</v>
+        <v>7063148</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4234,10 +4229,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122734570</v>
+        <v>122734679</v>
       </c>
       <c r="B35" t="n">
-        <v>90963</v>
+        <v>56680</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4246,38 +4241,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1205</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542057</v>
+        <v>542110</v>
       </c>
       <c r="R35" t="n">
-        <v>7063036</v>
+        <v>7063060</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734167</v>
+        <v>122733821</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4969,34 +4969,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541962</v>
+        <v>541894</v>
       </c>
       <c r="R42" t="n">
-        <v>7063054</v>
+        <v>7063121</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5055,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122733821</v>
+        <v>122734167</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5071,39 +5076,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541894</v>
+        <v>541962</v>
       </c>
       <c r="R43" t="n">
-        <v>7063121</v>
+        <v>7063054</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122735254</v>
+        <v>122734998</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5280,34 +5280,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542200</v>
+        <v>542180</v>
       </c>
       <c r="R45" t="n">
-        <v>7063362</v>
+        <v>7063280</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5366,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734998</v>
+        <v>122735254</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5382,39 +5387,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542180</v>
+        <v>542200</v>
       </c>
       <c r="R46" t="n">
-        <v>7063280</v>
+        <v>7063362</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122734184</v>
+        <v>122734480</v>
       </c>
       <c r="B50" t="n">
-        <v>97319</v>
+        <v>90963</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>1205</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541962</v>
+        <v>542012</v>
       </c>
       <c r="R50" t="n">
-        <v>7063054</v>
+        <v>7063013</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122734480</v>
+        <v>122734884</v>
       </c>
       <c r="B51" t="n">
-        <v>90963</v>
+        <v>90917</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542012</v>
+        <v>542151</v>
       </c>
       <c r="R51" t="n">
-        <v>7063013</v>
+        <v>7063216</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734884</v>
+        <v>122735437</v>
       </c>
       <c r="B52" t="n">
-        <v>90917</v>
+        <v>79875</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,21 +6019,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542151</v>
+        <v>542207</v>
       </c>
       <c r="R52" t="n">
-        <v>7063216</v>
+        <v>7063420</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122735437</v>
+        <v>122734184</v>
       </c>
       <c r="B53" t="n">
-        <v>79875</v>
+        <v>97319</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6121,21 +6121,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542207</v>
+        <v>541962</v>
       </c>
       <c r="R53" t="n">
-        <v>7063420</v>
+        <v>7063054</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122733563</v>
+        <v>122733445</v>
       </c>
       <c r="B54" t="n">
-        <v>88303</v>
+        <v>90917</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6219,25 +6219,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541868</v>
+        <v>541842</v>
       </c>
       <c r="R54" t="n">
-        <v>7063239</v>
+        <v>7063190</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122733946</v>
+        <v>122733563</v>
       </c>
       <c r="B55" t="n">
-        <v>74855</v>
+        <v>88303</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541887</v>
+        <v>541868</v>
       </c>
       <c r="R55" t="n">
-        <v>7063133</v>
+        <v>7063239</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6411,10 +6411,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122734495</v>
+        <v>122733946</v>
       </c>
       <c r="B56" t="n">
-        <v>79751</v>
+        <v>74855</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6423,25 +6423,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>542019</v>
+        <v>541887</v>
       </c>
       <c r="R56" t="n">
-        <v>7063019</v>
+        <v>7063133</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734127</v>
+        <v>122734495</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6525,25 +6525,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6553,10 +6553,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541949</v>
+        <v>542019</v>
       </c>
       <c r="R57" t="n">
-        <v>7063047</v>
+        <v>7063019</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6615,10 +6615,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122735514</v>
+        <v>122734127</v>
       </c>
       <c r="B58" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6627,25 +6627,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542225</v>
+        <v>541949</v>
       </c>
       <c r="R58" t="n">
-        <v>7063451</v>
+        <v>7063047</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122733445</v>
+        <v>122735514</v>
       </c>
       <c r="B59" t="n">
-        <v>90917</v>
+        <v>79882</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6733,21 +6733,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6757,10 +6757,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541842</v>
+        <v>542225</v>
       </c>
       <c r="R59" t="n">
-        <v>7063190</v>
+        <v>7063451</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -3710,10 +3710,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733859</v>
+        <v>122733400</v>
       </c>
       <c r="B30" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,38 +3722,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541895</v>
+        <v>541821</v>
       </c>
       <c r="R30" t="n">
-        <v>7063121</v>
+        <v>7063185</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3914,10 +3918,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122733400</v>
+        <v>122733859</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3926,42 +3930,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541821</v>
+        <v>541895</v>
       </c>
       <c r="R32" t="n">
-        <v>7063185</v>
+        <v>7063121</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122734559</v>
+        <v>122734932</v>
       </c>
       <c r="B36" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4348,25 +4348,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542051</v>
+        <v>542178</v>
       </c>
       <c r="R36" t="n">
-        <v>7063037</v>
+        <v>7063224</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4412,6 +4412,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122734932</v>
+        <v>122733626</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4454,21 +4459,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4478,10 +4483,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542178</v>
+        <v>541894</v>
       </c>
       <c r="R37" t="n">
-        <v>7063224</v>
+        <v>7063219</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4514,11 +4519,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,10 +4545,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122733412</v>
+        <v>122734232</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4557,25 +4557,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541827</v>
+        <v>541952</v>
       </c>
       <c r="R38" t="n">
-        <v>7063182</v>
+        <v>7063000</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122733626</v>
+        <v>122734559</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4659,25 +4659,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541894</v>
+        <v>542051</v>
       </c>
       <c r="R39" t="n">
-        <v>7063219</v>
+        <v>7063037</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4749,10 +4749,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734232</v>
+        <v>122733412</v>
       </c>
       <c r="B40" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4761,25 +4761,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541952</v>
+        <v>541827</v>
       </c>
       <c r="R40" t="n">
-        <v>7063000</v>
+        <v>7063182</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733821</v>
+        <v>122734167</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4969,39 +4969,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541894</v>
+        <v>541962</v>
       </c>
       <c r="R42" t="n">
-        <v>7063121</v>
+        <v>7063054</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5060,10 +5055,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734167</v>
+        <v>122733821</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5076,34 +5071,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541962</v>
+        <v>541894</v>
       </c>
       <c r="R43" t="n">
-        <v>7063054</v>
+        <v>7063121</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122734480</v>
+        <v>122734184</v>
       </c>
       <c r="B50" t="n">
-        <v>90963</v>
+        <v>97319</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542012</v>
+        <v>541962</v>
       </c>
       <c r="R50" t="n">
-        <v>7063013</v>
+        <v>7063054</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122734884</v>
+        <v>122734480</v>
       </c>
       <c r="B51" t="n">
-        <v>90917</v>
+        <v>90963</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542151</v>
+        <v>542012</v>
       </c>
       <c r="R51" t="n">
-        <v>7063216</v>
+        <v>7063013</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122735437</v>
+        <v>122734884</v>
       </c>
       <c r="B52" t="n">
-        <v>79875</v>
+        <v>90917</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,21 +6019,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542207</v>
+        <v>542151</v>
       </c>
       <c r="R52" t="n">
-        <v>7063420</v>
+        <v>7063216</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122734184</v>
+        <v>122735437</v>
       </c>
       <c r="B53" t="n">
-        <v>97319</v>
+        <v>79875</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6121,21 +6121,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541962</v>
+        <v>542207</v>
       </c>
       <c r="R53" t="n">
-        <v>7063054</v>
+        <v>7063420</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122733746</v>
+        <v>122734184</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>97319</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,39 +2049,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541904</v>
+        <v>541962</v>
       </c>
       <c r="R14" t="n">
-        <v>7063170</v>
+        <v>7063054</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2140,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122735193</v>
+        <v>122734661</v>
       </c>
       <c r="B15" t="n">
         <v>90917</v>
@@ -2180,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542209</v>
+        <v>542103</v>
       </c>
       <c r="R15" t="n">
-        <v>7063318</v>
+        <v>7063058</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2242,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733598</v>
+        <v>122733573</v>
       </c>
       <c r="B16" t="n">
         <v>56688</v>
@@ -2287,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541891</v>
+        <v>541859</v>
       </c>
       <c r="R16" t="n">
-        <v>7063227</v>
+        <v>7063245</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2349,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733611</v>
+        <v>122735514</v>
       </c>
       <c r="B17" t="n">
-        <v>56688</v>
+        <v>79882</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,39 +2360,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541894</v>
+        <v>542225</v>
       </c>
       <c r="R17" t="n">
-        <v>7063219</v>
+        <v>7063451</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2456,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122735805</v>
+        <v>122733859</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2472,39 +2462,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542199</v>
+        <v>541895</v>
       </c>
       <c r="R18" t="n">
-        <v>7063483</v>
+        <v>7063121</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2537,11 +2522,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734876</v>
+        <v>122735552</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,38 +2560,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542150</v>
+        <v>542188</v>
       </c>
       <c r="R19" t="n">
-        <v>7063210</v>
+        <v>7063472</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2670,10 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122735308</v>
+        <v>122733497</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,38 +2667,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542199</v>
+        <v>541868</v>
       </c>
       <c r="R20" t="n">
-        <v>7063368</v>
+        <v>7063207</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2772,7 +2762,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122734589</v>
+        <v>122734524</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2812,10 +2802,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542061</v>
+        <v>542051</v>
       </c>
       <c r="R21" t="n">
-        <v>7063040</v>
+        <v>7063037</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2874,7 +2864,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122740383</v>
+        <v>122735193</v>
       </c>
       <c r="B22" t="n">
         <v>90917</v>
@@ -2914,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542117</v>
+        <v>542209</v>
       </c>
       <c r="R22" t="n">
-        <v>7063503</v>
+        <v>7063318</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2976,7 +2966,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122734661</v>
+        <v>122734559</v>
       </c>
       <c r="B23" t="n">
         <v>90917</v>
@@ -3016,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542103</v>
+        <v>542051</v>
       </c>
       <c r="R23" t="n">
-        <v>7063058</v>
+        <v>7063037</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3078,7 +3068,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122735552</v>
+        <v>122733623</v>
       </c>
       <c r="B24" t="n">
         <v>56688</v>
@@ -3123,10 +3113,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542188</v>
+        <v>541894</v>
       </c>
       <c r="R24" t="n">
-        <v>7063472</v>
+        <v>7063219</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3185,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122733223</v>
+        <v>122734495</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>79751</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3201,39 +3191,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541808</v>
+        <v>542019</v>
       </c>
       <c r="R25" t="n">
-        <v>7063277</v>
+        <v>7063019</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122734549</v>
+        <v>122735308</v>
       </c>
       <c r="B26" t="n">
-        <v>56078</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3308,39 +3293,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542051</v>
+        <v>542199</v>
       </c>
       <c r="R26" t="n">
-        <v>7063037</v>
+        <v>7063368</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3399,7 +3379,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122735491</v>
+        <v>122733412</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3439,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542222</v>
+        <v>541827</v>
       </c>
       <c r="R27" t="n">
-        <v>7063450</v>
+        <v>7063182</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3501,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734625</v>
+        <v>122734679</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3517,34 +3497,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542072</v>
+        <v>542110</v>
       </c>
       <c r="R28" t="n">
-        <v>7063043</v>
+        <v>7063060</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3603,10 +3588,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733573</v>
+        <v>122733400</v>
       </c>
       <c r="B29" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,31 +3600,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3648,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541859</v>
+        <v>541821</v>
       </c>
       <c r="R29" t="n">
-        <v>7063245</v>
+        <v>7063185</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3710,10 +3694,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733400</v>
+        <v>122733563</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>88303</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,42 +3706,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541821</v>
+        <v>541868</v>
       </c>
       <c r="R30" t="n">
-        <v>7063185</v>
+        <v>7063239</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3816,7 +3796,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122734524</v>
+        <v>122734625</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -3856,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542051</v>
+        <v>542072</v>
       </c>
       <c r="R31" t="n">
-        <v>7063037</v>
+        <v>7063043</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3918,10 +3898,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122733859</v>
+        <v>122734737</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3930,38 +3910,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541895</v>
+        <v>542156</v>
       </c>
       <c r="R32" t="n">
-        <v>7063121</v>
+        <v>7063148</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4020,10 +4005,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734570</v>
+        <v>122734693</v>
       </c>
       <c r="B33" t="n">
-        <v>90963</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4032,25 +4017,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4060,10 +4045,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542057</v>
+        <v>542111</v>
       </c>
       <c r="R33" t="n">
-        <v>7063036</v>
+        <v>7063060</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4122,10 +4107,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734737</v>
+        <v>122734570</v>
       </c>
       <c r="B34" t="n">
-        <v>56688</v>
+        <v>90963</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,39 +4123,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542156</v>
+        <v>542057</v>
       </c>
       <c r="R34" t="n">
-        <v>7063148</v>
+        <v>7063036</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4229,10 +4209,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122734679</v>
+        <v>122734709</v>
       </c>
       <c r="B35" t="n">
-        <v>56680</v>
+        <v>91397</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4241,43 +4221,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542110</v>
+        <v>542116</v>
       </c>
       <c r="R35" t="n">
-        <v>7063060</v>
+        <v>7063065</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4336,10 +4311,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122734932</v>
+        <v>122734167</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4352,21 +4327,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4376,10 +4351,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542178</v>
+        <v>541962</v>
       </c>
       <c r="R36" t="n">
-        <v>7063224</v>
+        <v>7063054</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4412,11 +4387,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,10 +4413,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122733626</v>
+        <v>122735437</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>79875</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4455,25 +4425,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4483,10 +4453,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541894</v>
+        <v>542207</v>
       </c>
       <c r="R37" t="n">
-        <v>7063219</v>
+        <v>7063420</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4545,10 +4515,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122734232</v>
+        <v>122734433</v>
       </c>
       <c r="B38" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4557,25 +4527,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4585,10 +4555,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541952</v>
+        <v>542016</v>
       </c>
       <c r="R38" t="n">
-        <v>7063000</v>
+        <v>7063029</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4647,10 +4617,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122734559</v>
+        <v>122734932</v>
       </c>
       <c r="B39" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4659,25 +4629,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4687,10 +4657,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542051</v>
+        <v>542178</v>
       </c>
       <c r="R39" t="n">
-        <v>7063037</v>
+        <v>7063224</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4723,6 +4693,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4749,7 +4724,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122733412</v>
+        <v>122734876</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -4789,10 +4764,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541827</v>
+        <v>542150</v>
       </c>
       <c r="R40" t="n">
-        <v>7063182</v>
+        <v>7063210</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4851,10 +4826,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734693</v>
+        <v>122733223</v>
       </c>
       <c r="B41" t="n">
-        <v>90952</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4863,38 +4838,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542111</v>
+        <v>541808</v>
       </c>
       <c r="R41" t="n">
-        <v>7063060</v>
+        <v>7063277</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4953,10 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734167</v>
+        <v>122734998</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4969,34 +4949,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541962</v>
+        <v>542180</v>
       </c>
       <c r="R42" t="n">
-        <v>7063054</v>
+        <v>7063280</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5055,10 +5040,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122733821</v>
+        <v>122734480</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>90963</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5067,43 +5052,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541894</v>
+        <v>542012</v>
       </c>
       <c r="R43" t="n">
-        <v>7063121</v>
+        <v>7063013</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5162,10 +5142,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122735524</v>
+        <v>122733746</v>
       </c>
       <c r="B44" t="n">
-        <v>79876</v>
+        <v>56688</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5178,34 +5158,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542224</v>
+        <v>541904</v>
       </c>
       <c r="R44" t="n">
-        <v>7063455</v>
+        <v>7063170</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5264,10 +5249,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122734998</v>
+        <v>122735145</v>
       </c>
       <c r="B45" t="n">
-        <v>57631</v>
+        <v>90952</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5280,39 +5265,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542180</v>
+        <v>542201</v>
       </c>
       <c r="R45" t="n">
-        <v>7063280</v>
+        <v>7063315</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5371,10 +5351,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122735254</v>
+        <v>122740383</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,25 +5363,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5391,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542200</v>
+        <v>542117</v>
       </c>
       <c r="R46" t="n">
-        <v>7063362</v>
+        <v>7063503</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5473,10 +5453,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122734094</v>
+        <v>122733598</v>
       </c>
       <c r="B47" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5485,31 +5465,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5518,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541918</v>
+        <v>541891</v>
       </c>
       <c r="R47" t="n">
-        <v>7063050</v>
+        <v>7063227</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5580,7 +5560,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122733348</v>
+        <v>122733368</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5692,10 +5672,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122733497</v>
+        <v>122734191</v>
       </c>
       <c r="B49" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5704,43 +5684,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541868</v>
+        <v>541959</v>
       </c>
       <c r="R49" t="n">
-        <v>7063207</v>
+        <v>7063011</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5799,10 +5774,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122734184</v>
+        <v>122734589</v>
       </c>
       <c r="B50" t="n">
-        <v>97319</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5811,25 +5786,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5839,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541962</v>
+        <v>542061</v>
       </c>
       <c r="R50" t="n">
-        <v>7063054</v>
+        <v>7063040</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5901,10 +5876,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122734480</v>
+        <v>122735805</v>
       </c>
       <c r="B51" t="n">
-        <v>90963</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5888,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542012</v>
+        <v>542199</v>
       </c>
       <c r="R51" t="n">
-        <v>7063013</v>
+        <v>7063483</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5977,6 +5957,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6003,10 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734884</v>
+        <v>122734549</v>
       </c>
       <c r="B52" t="n">
-        <v>90917</v>
+        <v>56078</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6015,38 +6000,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542151</v>
+        <v>542051</v>
       </c>
       <c r="R52" t="n">
-        <v>7063216</v>
+        <v>7063037</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6105,10 +6095,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122735437</v>
+        <v>122735524</v>
       </c>
       <c r="B53" t="n">
-        <v>79875</v>
+        <v>79876</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6121,21 +6111,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6145,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542207</v>
+        <v>542224</v>
       </c>
       <c r="R53" t="n">
-        <v>7063420</v>
+        <v>7063455</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6207,10 +6197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122733445</v>
+        <v>122734614</v>
       </c>
       <c r="B54" t="n">
-        <v>90917</v>
+        <v>79882</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6223,21 +6213,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6247,10 +6237,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541842</v>
+        <v>542075</v>
       </c>
       <c r="R54" t="n">
-        <v>7063190</v>
+        <v>7063031</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6309,10 +6299,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122733563</v>
+        <v>122733445</v>
       </c>
       <c r="B55" t="n">
-        <v>88303</v>
+        <v>90917</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6321,25 +6311,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6349,10 +6339,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541868</v>
+        <v>541842</v>
       </c>
       <c r="R55" t="n">
-        <v>7063239</v>
+        <v>7063190</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6411,10 +6401,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122733946</v>
+        <v>122733821</v>
       </c>
       <c r="B56" t="n">
-        <v>74855</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6427,34 +6417,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541887</v>
+        <v>541894</v>
       </c>
       <c r="R56" t="n">
-        <v>7063133</v>
+        <v>7063121</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6513,10 +6508,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734495</v>
+        <v>122733946</v>
       </c>
       <c r="B57" t="n">
-        <v>79751</v>
+        <v>74855</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6525,25 +6520,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6553,10 +6548,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>542019</v>
+        <v>541887</v>
       </c>
       <c r="R57" t="n">
-        <v>7063019</v>
+        <v>7063133</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6615,10 +6610,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122734127</v>
+        <v>122735414</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6631,34 +6626,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541949</v>
+        <v>542209</v>
       </c>
       <c r="R58" t="n">
-        <v>7063047</v>
+        <v>7063388</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6691,6 +6691,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6717,10 +6722,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122735514</v>
+        <v>122735491</v>
       </c>
       <c r="B59" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6729,25 +6734,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6757,10 +6762,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542225</v>
+        <v>542222</v>
       </c>
       <c r="R59" t="n">
-        <v>7063451</v>
+        <v>7063450</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6819,10 +6824,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122734614</v>
+        <v>122733626</v>
       </c>
       <c r="B60" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6831,25 +6836,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6859,10 +6864,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542075</v>
+        <v>541894</v>
       </c>
       <c r="R60" t="n">
-        <v>7063031</v>
+        <v>7063219</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6921,10 +6926,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122735414</v>
+        <v>122734094</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6937,16 +6942,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6957,7 +6962,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6966,10 +6971,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>542209</v>
+        <v>541918</v>
       </c>
       <c r="R61" t="n">
-        <v>7063388</v>
+        <v>7063050</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7002,11 +7007,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122734709</v>
+        <v>122734127</v>
       </c>
       <c r="B63" t="n">
-        <v>91397</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7151,25 +7151,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542116</v>
+        <v>541949</v>
       </c>
       <c r="R63" t="n">
-        <v>7063065</v>
+        <v>7063047</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122735145</v>
+        <v>122735254</v>
       </c>
       <c r="B64" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7257,21 +7257,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542201</v>
+        <v>542200</v>
       </c>
       <c r="R64" t="n">
-        <v>7063315</v>
+        <v>7063362</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7343,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122734433</v>
+        <v>122734884</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7355,25 +7355,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542016</v>
+        <v>542151</v>
       </c>
       <c r="R65" t="n">
-        <v>7063029</v>
+        <v>7063216</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7445,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122734191</v>
+        <v>122734232</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7457,25 +7457,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7485,10 +7485,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541959</v>
+        <v>541952</v>
       </c>
       <c r="R66" t="n">
-        <v>7063011</v>
+        <v>7063000</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122734184</v>
+        <v>122735193</v>
       </c>
       <c r="B14" t="n">
-        <v>97319</v>
+        <v>90917</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541962</v>
+        <v>542209</v>
       </c>
       <c r="R14" t="n">
-        <v>7063054</v>
+        <v>7063318</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122734661</v>
+        <v>122733598</v>
       </c>
       <c r="B15" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,34 +2151,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542103</v>
+        <v>541891</v>
       </c>
       <c r="R15" t="n">
-        <v>7063058</v>
+        <v>7063227</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2237,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733573</v>
+        <v>122733626</v>
       </c>
       <c r="B16" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,43 +2254,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541859</v>
+        <v>541894</v>
       </c>
       <c r="R16" t="n">
-        <v>7063245</v>
+        <v>7063219</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122735514</v>
+        <v>122733368</v>
       </c>
       <c r="B17" t="n">
-        <v>79882</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,38 +2356,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542225</v>
+        <v>541796</v>
       </c>
       <c r="R17" t="n">
-        <v>7063451</v>
+        <v>7063200</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2420,6 +2425,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,10 +2456,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122733859</v>
+        <v>122734524</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2462,21 +2472,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541895</v>
+        <v>542051</v>
       </c>
       <c r="R18" t="n">
-        <v>7063121</v>
+        <v>7063037</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2548,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122735552</v>
+        <v>122734480</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>90963</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,39 +2574,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542188</v>
+        <v>542012</v>
       </c>
       <c r="R19" t="n">
-        <v>7063472</v>
+        <v>7063013</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2655,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122733497</v>
+        <v>122734884</v>
       </c>
       <c r="B20" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,39 +2676,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541868</v>
+        <v>542151</v>
       </c>
       <c r="R20" t="n">
-        <v>7063207</v>
+        <v>7063216</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122734524</v>
+        <v>122735514</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,25 +2774,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2802,10 +2802,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542051</v>
+        <v>542225</v>
       </c>
       <c r="R21" t="n">
-        <v>7063037</v>
+        <v>7063451</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122735193</v>
+        <v>122734614</v>
       </c>
       <c r="B22" t="n">
-        <v>90917</v>
+        <v>79882</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2880,21 +2880,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542209</v>
+        <v>542075</v>
       </c>
       <c r="R22" t="n">
-        <v>7063318</v>
+        <v>7063031</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122734559</v>
+        <v>122733223</v>
       </c>
       <c r="B23" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2982,34 +2982,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542051</v>
+        <v>541808</v>
       </c>
       <c r="R23" t="n">
-        <v>7063037</v>
+        <v>7063277</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3068,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122733623</v>
+        <v>122733563</v>
       </c>
       <c r="B24" t="n">
-        <v>56688</v>
+        <v>88303</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,43 +3085,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541894</v>
+        <v>541868</v>
       </c>
       <c r="R24" t="n">
-        <v>7063219</v>
+        <v>7063239</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3175,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122734495</v>
+        <v>122733821</v>
       </c>
       <c r="B25" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,38 +3187,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542019</v>
+        <v>541894</v>
       </c>
       <c r="R25" t="n">
-        <v>7063019</v>
+        <v>7063121</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3277,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122735308</v>
+        <v>122734661</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3289,25 +3294,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3317,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542199</v>
+        <v>542103</v>
       </c>
       <c r="R26" t="n">
-        <v>7063368</v>
+        <v>7063058</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3379,10 +3384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122733412</v>
+        <v>122735552</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,38 +3396,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541827</v>
+        <v>542188</v>
       </c>
       <c r="R27" t="n">
-        <v>7063182</v>
+        <v>7063472</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3481,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734679</v>
+        <v>122733445</v>
       </c>
       <c r="B28" t="n">
-        <v>56680</v>
+        <v>90917</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3493,43 +3503,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542110</v>
+        <v>541842</v>
       </c>
       <c r="R28" t="n">
-        <v>7063060</v>
+        <v>7063190</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3588,10 +3593,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733400</v>
+        <v>122734625</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3600,42 +3605,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541821</v>
+        <v>542072</v>
       </c>
       <c r="R29" t="n">
-        <v>7063185</v>
+        <v>7063043</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3694,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733563</v>
+        <v>122733412</v>
       </c>
       <c r="B30" t="n">
-        <v>88303</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,21 +3711,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541868</v>
+        <v>541827</v>
       </c>
       <c r="R30" t="n">
-        <v>7063239</v>
+        <v>7063182</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3796,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122734625</v>
+        <v>122734998</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,34 +3813,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542072</v>
+        <v>542180</v>
       </c>
       <c r="R31" t="n">
-        <v>7063043</v>
+        <v>7063280</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3898,10 +3904,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122734737</v>
+        <v>122735524</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>79876</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,39 +3920,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542156</v>
+        <v>542224</v>
       </c>
       <c r="R32" t="n">
-        <v>7063148</v>
+        <v>7063455</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4005,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734693</v>
+        <v>122734495</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>79751</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,25 +4018,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4045,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542111</v>
+        <v>542019</v>
       </c>
       <c r="R33" t="n">
-        <v>7063060</v>
+        <v>7063019</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4107,10 +4108,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734570</v>
+        <v>122734932</v>
       </c>
       <c r="B34" t="n">
-        <v>90963</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4119,25 +4120,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4147,10 +4148,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542057</v>
+        <v>542178</v>
       </c>
       <c r="R34" t="n">
-        <v>7063036</v>
+        <v>7063224</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4183,6 +4184,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122734709</v>
+        <v>122735145</v>
       </c>
       <c r="B35" t="n">
-        <v>91397</v>
+        <v>90952</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4221,25 +4227,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4249,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542116</v>
+        <v>542201</v>
       </c>
       <c r="R35" t="n">
-        <v>7063065</v>
+        <v>7063315</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4311,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122734167</v>
+        <v>122733946</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>74855</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4327,21 +4333,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4351,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541962</v>
+        <v>541887</v>
       </c>
       <c r="R36" t="n">
-        <v>7063054</v>
+        <v>7063133</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4413,10 +4419,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122735437</v>
+        <v>122734433</v>
       </c>
       <c r="B37" t="n">
-        <v>79875</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4425,25 +4431,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4453,10 +4459,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542207</v>
+        <v>542016</v>
       </c>
       <c r="R37" t="n">
-        <v>7063420</v>
+        <v>7063029</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4515,10 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122734433</v>
+        <v>122734184</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>97319</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4527,25 +4533,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4555,10 +4561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542016</v>
+        <v>541962</v>
       </c>
       <c r="R38" t="n">
-        <v>7063029</v>
+        <v>7063054</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4617,10 +4623,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122734932</v>
+        <v>122735254</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4633,21 +4639,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4657,10 +4663,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542178</v>
+        <v>542200</v>
       </c>
       <c r="R39" t="n">
-        <v>7063224</v>
+        <v>7063362</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4693,11 +4699,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4724,7 +4725,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734876</v>
+        <v>122734589</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -4764,10 +4765,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542150</v>
+        <v>542061</v>
       </c>
       <c r="R40" t="n">
-        <v>7063210</v>
+        <v>7063040</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4826,10 +4827,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122733223</v>
+        <v>122734709</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>91397</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4838,43 +4839,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541808</v>
+        <v>542116</v>
       </c>
       <c r="R41" t="n">
-        <v>7063277</v>
+        <v>7063065</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4933,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734998</v>
+        <v>122734559</v>
       </c>
       <c r="B42" t="n">
-        <v>57631</v>
+        <v>90917</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4945,43 +4941,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542180</v>
+        <v>542051</v>
       </c>
       <c r="R42" t="n">
-        <v>7063280</v>
+        <v>7063037</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5040,10 +5031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734480</v>
+        <v>122734094</v>
       </c>
       <c r="B43" t="n">
-        <v>90963</v>
+        <v>57494</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5052,38 +5043,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542012</v>
+        <v>541918</v>
       </c>
       <c r="R43" t="n">
-        <v>7063013</v>
+        <v>7063050</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5142,10 +5138,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122733746</v>
+        <v>122733400</v>
       </c>
       <c r="B44" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5154,31 +5150,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5187,10 +5182,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541904</v>
+        <v>541821</v>
       </c>
       <c r="R44" t="n">
-        <v>7063170</v>
+        <v>7063185</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5249,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122735145</v>
+        <v>122734549</v>
       </c>
       <c r="B45" t="n">
-        <v>90952</v>
+        <v>56078</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5265,34 +5260,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542201</v>
+        <v>542051</v>
       </c>
       <c r="R45" t="n">
-        <v>7063315</v>
+        <v>7063037</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122740383</v>
+        <v>122735308</v>
       </c>
       <c r="B46" t="n">
-        <v>90917</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5363,25 +5363,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542117</v>
+        <v>542199</v>
       </c>
       <c r="R46" t="n">
-        <v>7063503</v>
+        <v>7063368</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5453,7 +5453,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122733598</v>
+        <v>122733573</v>
       </c>
       <c r="B47" t="n">
         <v>56688</v>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541891</v>
+        <v>541859</v>
       </c>
       <c r="R47" t="n">
-        <v>7063227</v>
+        <v>7063245</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122733368</v>
+        <v>122733859</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5576,39 +5576,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541796</v>
+        <v>541895</v>
       </c>
       <c r="R48" t="n">
-        <v>7063200</v>
+        <v>7063121</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5641,11 +5636,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,7 +5662,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122734191</v>
+        <v>122735491</v>
       </c>
       <c r="B49" t="n">
         <v>79847</v>
@@ -5712,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541959</v>
+        <v>542222</v>
       </c>
       <c r="R49" t="n">
-        <v>7063011</v>
+        <v>7063450</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5774,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122734589</v>
+        <v>122735805</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5790,34 +5780,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542061</v>
+        <v>542199</v>
       </c>
       <c r="R50" t="n">
-        <v>7063040</v>
+        <v>7063483</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5850,6 +5845,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5876,10 +5876,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122735805</v>
+        <v>122733746</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5888,31 +5888,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542199</v>
+        <v>541904</v>
       </c>
       <c r="R51" t="n">
-        <v>7063483</v>
+        <v>7063170</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5957,11 +5957,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5988,10 +5983,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734549</v>
+        <v>122734693</v>
       </c>
       <c r="B52" t="n">
-        <v>56078</v>
+        <v>90952</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6004,39 +5999,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542051</v>
+        <v>542111</v>
       </c>
       <c r="R52" t="n">
-        <v>7063037</v>
+        <v>7063060</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6095,10 +6085,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122735524</v>
+        <v>122735414</v>
       </c>
       <c r="B53" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6107,38 +6097,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542224</v>
+        <v>542209</v>
       </c>
       <c r="R53" t="n">
-        <v>7063455</v>
+        <v>7063388</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6171,6 +6166,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6197,10 +6197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122734614</v>
+        <v>122735437</v>
       </c>
       <c r="B54" t="n">
-        <v>79882</v>
+        <v>79875</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542075</v>
+        <v>542207</v>
       </c>
       <c r="R54" t="n">
-        <v>7063031</v>
+        <v>7063420</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6299,10 +6299,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122733445</v>
+        <v>122734876</v>
       </c>
       <c r="B55" t="n">
-        <v>90917</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6311,25 +6311,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541842</v>
+        <v>542150</v>
       </c>
       <c r="R55" t="n">
-        <v>7063190</v>
+        <v>7063210</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6401,10 +6401,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122733821</v>
+        <v>122734167</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6417,39 +6417,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541894</v>
+        <v>541962</v>
       </c>
       <c r="R56" t="n">
-        <v>7063121</v>
+        <v>7063054</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6508,10 +6503,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122733946</v>
+        <v>122734127</v>
       </c>
       <c r="B57" t="n">
-        <v>74855</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6524,21 +6519,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6548,10 +6543,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541887</v>
+        <v>541949</v>
       </c>
       <c r="R57" t="n">
-        <v>7063133</v>
+        <v>7063047</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6610,10 +6605,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122735414</v>
+        <v>122734191</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6626,39 +6621,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542209</v>
+        <v>541959</v>
       </c>
       <c r="R58" t="n">
-        <v>7063388</v>
+        <v>7063011</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6691,11 +6681,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6722,10 +6707,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122735491</v>
+        <v>122733611</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6734,38 +6719,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542222</v>
+        <v>541894</v>
       </c>
       <c r="R59" t="n">
-        <v>7063450</v>
+        <v>7063219</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6824,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122733626</v>
+        <v>122734679</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6840,34 +6830,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541894</v>
+        <v>542110</v>
       </c>
       <c r="R60" t="n">
-        <v>7063219</v>
+        <v>7063060</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6926,10 +6921,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122734094</v>
+        <v>122734232</v>
       </c>
       <c r="B61" t="n">
-        <v>57494</v>
+        <v>79883</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6938,43 +6933,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541918</v>
+        <v>541952</v>
       </c>
       <c r="R61" t="n">
-        <v>7063050</v>
+        <v>7063000</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7033,10 +7023,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122733654</v>
+        <v>122734570</v>
       </c>
       <c r="B62" t="n">
-        <v>79718</v>
+        <v>90963</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7045,41 +7035,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>389</v>
+        <v>1205</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541896</v>
+        <v>542057</v>
       </c>
       <c r="R62" t="n">
-        <v>7063207</v>
+        <v>7063036</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7120,7 +7107,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7139,10 +7125,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122734127</v>
+        <v>122734737</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7151,38 +7137,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541949</v>
+        <v>542156</v>
       </c>
       <c r="R63" t="n">
-        <v>7063047</v>
+        <v>7063148</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7241,10 +7232,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122735254</v>
+        <v>122740383</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7253,25 +7244,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7281,10 +7272,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542200</v>
+        <v>542117</v>
       </c>
       <c r="R64" t="n">
-        <v>7063362</v>
+        <v>7063503</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7343,10 +7334,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122734884</v>
+        <v>122733654</v>
       </c>
       <c r="B65" t="n">
-        <v>90917</v>
+        <v>79718</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7355,38 +7346,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>389</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542151</v>
+        <v>541896</v>
       </c>
       <c r="R65" t="n">
-        <v>7063216</v>
+        <v>7063207</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7427,6 +7421,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7445,10 +7440,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122734232</v>
+        <v>122733497</v>
       </c>
       <c r="B66" t="n">
-        <v>79883</v>
+        <v>56688</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7461,34 +7456,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541952</v>
+        <v>541868</v>
       </c>
       <c r="R66" t="n">
-        <v>7063000</v>
+        <v>7063207</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122733598</v>
+        <v>122733626</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,43 +2147,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541891</v>
+        <v>541894</v>
       </c>
       <c r="R15" t="n">
-        <v>7063227</v>
+        <v>7063219</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733626</v>
+        <v>122733368</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,34 +2253,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541894</v>
+        <v>541796</v>
       </c>
       <c r="R16" t="n">
-        <v>7063219</v>
+        <v>7063200</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2318,6 +2318,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733368</v>
+        <v>122733598</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,31 +2361,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2389,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541796</v>
+        <v>541891</v>
       </c>
       <c r="R17" t="n">
-        <v>7063200</v>
+        <v>7063227</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2425,11 +2430,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734480</v>
+        <v>122734884</v>
       </c>
       <c r="B19" t="n">
-        <v>90963</v>
+        <v>90917</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542012</v>
+        <v>542151</v>
       </c>
       <c r="R19" t="n">
-        <v>7063013</v>
+        <v>7063216</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734884</v>
+        <v>122734480</v>
       </c>
       <c r="B20" t="n">
-        <v>90917</v>
+        <v>90963</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542151</v>
+        <v>542012</v>
       </c>
       <c r="R20" t="n">
-        <v>7063216</v>
+        <v>7063013</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122733445</v>
+        <v>122734998</v>
       </c>
       <c r="B28" t="n">
-        <v>90917</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3503,38 +3503,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541842</v>
+        <v>542180</v>
       </c>
       <c r="R28" t="n">
-        <v>7063190</v>
+        <v>7063280</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3593,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122734625</v>
+        <v>122733445</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3605,25 +3610,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3633,10 +3638,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542072</v>
+        <v>541842</v>
       </c>
       <c r="R29" t="n">
-        <v>7063043</v>
+        <v>7063190</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3695,7 +3700,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122733412</v>
+        <v>122734625</v>
       </c>
       <c r="B30" t="n">
         <v>79847</v>
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541827</v>
+        <v>542072</v>
       </c>
       <c r="R30" t="n">
-        <v>7063182</v>
+        <v>7063043</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3797,10 +3802,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122734998</v>
+        <v>122733412</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3813,39 +3818,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542180</v>
+        <v>541827</v>
       </c>
       <c r="R31" t="n">
-        <v>7063280</v>
+        <v>7063182</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122733400</v>
+        <v>122734549</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>56078</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,30 +5150,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5182,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541821</v>
+        <v>542051</v>
       </c>
       <c r="R44" t="n">
-        <v>7063185</v>
+        <v>7063037</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5244,10 +5245,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122734549</v>
+        <v>122733400</v>
       </c>
       <c r="B45" t="n">
-        <v>56078</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5256,31 +5257,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542051</v>
+        <v>541821</v>
       </c>
       <c r="R45" t="n">
-        <v>7063037</v>
+        <v>7063185</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122733626</v>
+        <v>122733598</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,38 +2147,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541894</v>
+        <v>541891</v>
       </c>
       <c r="R15" t="n">
-        <v>7063219</v>
+        <v>7063227</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2237,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733368</v>
+        <v>122733626</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,39 +2258,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541796</v>
+        <v>541894</v>
       </c>
       <c r="R16" t="n">
-        <v>7063200</v>
+        <v>7063219</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2318,11 +2318,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2349,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733598</v>
+        <v>122733368</v>
       </c>
       <c r="B17" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,31 +2356,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2394,10 +2389,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541891</v>
+        <v>541796</v>
       </c>
       <c r="R17" t="n">
-        <v>7063227</v>
+        <v>7063200</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2430,6 +2425,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122735193</v>
+        <v>122734570</v>
       </c>
       <c r="B14" t="n">
-        <v>90917</v>
+        <v>90966</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542209</v>
+        <v>542057</v>
       </c>
       <c r="R14" t="n">
-        <v>7063318</v>
+        <v>7063036</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122733598</v>
+        <v>122734709</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>91400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,43 +2147,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541891</v>
+        <v>542116</v>
       </c>
       <c r="R15" t="n">
-        <v>7063227</v>
+        <v>7063065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733626</v>
+        <v>122734524</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541894</v>
+        <v>542051</v>
       </c>
       <c r="R16" t="n">
-        <v>7063219</v>
+        <v>7063037</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2344,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733368</v>
+        <v>122733573</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>56691</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,31 +2351,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541796</v>
+        <v>541859</v>
       </c>
       <c r="R17" t="n">
-        <v>7063200</v>
+        <v>7063245</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2425,11 +2420,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734524</v>
+        <v>122734998</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>57634</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2472,34 +2462,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542051</v>
+        <v>542180</v>
       </c>
       <c r="R18" t="n">
-        <v>7063037</v>
+        <v>7063280</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2558,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122734884</v>
+        <v>122735254</v>
       </c>
       <c r="B19" t="n">
-        <v>90917</v>
+        <v>79850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,25 +2565,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542151</v>
+        <v>542200</v>
       </c>
       <c r="R19" t="n">
-        <v>7063216</v>
+        <v>7063362</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2660,10 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734480</v>
+        <v>122734559</v>
       </c>
       <c r="B20" t="n">
-        <v>90963</v>
+        <v>90920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2676,21 +2671,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2700,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542012</v>
+        <v>542051</v>
       </c>
       <c r="R20" t="n">
-        <v>7063013</v>
+        <v>7063037</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2762,10 +2757,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122735514</v>
+        <v>122733623</v>
       </c>
       <c r="B21" t="n">
-        <v>79882</v>
+        <v>56691</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2778,34 +2773,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542225</v>
+        <v>541894</v>
       </c>
       <c r="R21" t="n">
-        <v>7063451</v>
+        <v>7063219</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122734614</v>
+        <v>122735145</v>
       </c>
       <c r="B22" t="n">
-        <v>79882</v>
+        <v>90955</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,25 +2876,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542075</v>
+        <v>542201</v>
       </c>
       <c r="R22" t="n">
-        <v>7063031</v>
+        <v>7063315</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122733223</v>
+        <v>122733412</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>79850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,43 +2978,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541808</v>
+        <v>541827</v>
       </c>
       <c r="R23" t="n">
-        <v>7063277</v>
+        <v>7063182</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3073,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122733563</v>
+        <v>122733348</v>
       </c>
       <c r="B24" t="n">
-        <v>88303</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3089,34 +3084,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541868</v>
+        <v>541796</v>
       </c>
       <c r="R24" t="n">
-        <v>7063239</v>
+        <v>7063200</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3149,6 +3149,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122733821</v>
+        <v>122733746</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,31 +3192,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3220,10 +3225,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541894</v>
+        <v>541904</v>
       </c>
       <c r="R25" t="n">
-        <v>7063121</v>
+        <v>7063170</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3282,10 +3287,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122734661</v>
+        <v>122734232</v>
       </c>
       <c r="B26" t="n">
-        <v>90917</v>
+        <v>79886</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,21 +3303,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3322,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542103</v>
+        <v>541952</v>
       </c>
       <c r="R26" t="n">
-        <v>7063058</v>
+        <v>7063000</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3384,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122735552</v>
+        <v>122734094</v>
       </c>
       <c r="B27" t="n">
-        <v>56688</v>
+        <v>57497</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3396,31 +3401,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3429,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542188</v>
+        <v>541918</v>
       </c>
       <c r="R27" t="n">
-        <v>7063472</v>
+        <v>7063050</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3491,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122734998</v>
+        <v>122735491</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>79850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3507,39 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542180</v>
+        <v>542222</v>
       </c>
       <c r="R28" t="n">
-        <v>7063280</v>
+        <v>7063450</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3598,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733445</v>
+        <v>122734884</v>
       </c>
       <c r="B29" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541842</v>
+        <v>542151</v>
       </c>
       <c r="R29" t="n">
-        <v>7063190</v>
+        <v>7063216</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3700,10 +3700,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122734625</v>
+        <v>122734589</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542072</v>
+        <v>542061</v>
       </c>
       <c r="R30" t="n">
-        <v>7063043</v>
+        <v>7063040</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122733412</v>
+        <v>122733223</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>56691</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3814,38 +3814,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541827</v>
+        <v>541808</v>
       </c>
       <c r="R31" t="n">
-        <v>7063182</v>
+        <v>7063277</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3904,10 +3909,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122735524</v>
+        <v>122734495</v>
       </c>
       <c r="B32" t="n">
-        <v>79876</v>
+        <v>79754</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3920,21 +3925,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3944,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542224</v>
+        <v>542019</v>
       </c>
       <c r="R32" t="n">
-        <v>7063455</v>
+        <v>7063019</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4006,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122734495</v>
+        <v>122740383</v>
       </c>
       <c r="B33" t="n">
-        <v>79751</v>
+        <v>90920</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4022,21 +4027,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542019</v>
+        <v>542117</v>
       </c>
       <c r="R33" t="n">
-        <v>7063019</v>
+        <v>7063503</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4108,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734932</v>
+        <v>122734127</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4124,21 +4129,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4148,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542178</v>
+        <v>541949</v>
       </c>
       <c r="R34" t="n">
-        <v>7063224</v>
+        <v>7063047</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4184,11 +4189,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4215,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122735145</v>
+        <v>122734693</v>
       </c>
       <c r="B35" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542201</v>
+        <v>542111</v>
       </c>
       <c r="R35" t="n">
-        <v>7063315</v>
+        <v>7063060</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122733946</v>
+        <v>122735552</v>
       </c>
       <c r="B36" t="n">
-        <v>74855</v>
+        <v>56691</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4329,38 +4329,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541887</v>
+        <v>542188</v>
       </c>
       <c r="R36" t="n">
-        <v>7063133</v>
+        <v>7063472</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4419,10 +4424,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122734433</v>
+        <v>122735514</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>79885</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4431,25 +4436,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4459,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542016</v>
+        <v>542225</v>
       </c>
       <c r="R37" t="n">
-        <v>7063029</v>
+        <v>7063451</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4521,10 +4526,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122734184</v>
+        <v>122733859</v>
       </c>
       <c r="B38" t="n">
-        <v>97319</v>
+        <v>90955</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4533,25 +4538,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4561,10 +4566,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541962</v>
+        <v>541895</v>
       </c>
       <c r="R38" t="n">
-        <v>7063054</v>
+        <v>7063121</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4623,10 +4628,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122735254</v>
+        <v>122734679</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>56683</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4639,34 +4644,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542200</v>
+        <v>542110</v>
       </c>
       <c r="R39" t="n">
-        <v>7063362</v>
+        <v>7063060</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4725,10 +4735,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734589</v>
+        <v>122734625</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542061</v>
+        <v>542072</v>
       </c>
       <c r="R40" t="n">
-        <v>7063040</v>
+        <v>7063043</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4827,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122734709</v>
+        <v>122735805</v>
       </c>
       <c r="B41" t="n">
-        <v>91397</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4839,38 +4849,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542116</v>
+        <v>542199</v>
       </c>
       <c r="R41" t="n">
-        <v>7063065</v>
+        <v>7063483</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4903,6 +4918,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,10 +4949,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122734559</v>
+        <v>122733598</v>
       </c>
       <c r="B42" t="n">
-        <v>90917</v>
+        <v>56691</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4945,34 +4965,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542051</v>
+        <v>541891</v>
       </c>
       <c r="R42" t="n">
-        <v>7063037</v>
+        <v>7063227</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5031,10 +5056,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122734094</v>
+        <v>122733497</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>56691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,31 +5068,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5076,10 +5101,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541918</v>
+        <v>541868</v>
       </c>
       <c r="R43" t="n">
-        <v>7063050</v>
+        <v>7063207</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5138,10 +5163,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122734549</v>
+        <v>122733563</v>
       </c>
       <c r="B44" t="n">
-        <v>56078</v>
+        <v>88306</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5154,39 +5179,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542051</v>
+        <v>541868</v>
       </c>
       <c r="R44" t="n">
-        <v>7063037</v>
+        <v>7063239</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5245,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122733400</v>
+        <v>122733654</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>79721</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5261,38 +5281,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>389</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541821</v>
+        <v>541896</v>
       </c>
       <c r="R45" t="n">
-        <v>7063185</v>
+        <v>7063207</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5333,6 +5352,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5351,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122735308</v>
+        <v>122734549</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>56081</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,34 +5387,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542199</v>
+        <v>542051</v>
       </c>
       <c r="R46" t="n">
-        <v>7063368</v>
+        <v>7063037</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5453,10 +5478,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122733573</v>
+        <v>122734480</v>
       </c>
       <c r="B47" t="n">
-        <v>56688</v>
+        <v>90966</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,39 +5494,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541859</v>
+        <v>542012</v>
       </c>
       <c r="R47" t="n">
-        <v>7063245</v>
+        <v>7063013</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5560,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122733859</v>
+        <v>122734932</v>
       </c>
       <c r="B48" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5576,21 +5596,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5600,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541895</v>
+        <v>542178</v>
       </c>
       <c r="R48" t="n">
-        <v>7063121</v>
+        <v>7063224</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5636,6 +5656,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5662,10 +5687,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122735491</v>
+        <v>122735414</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5678,34 +5703,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542222</v>
+        <v>542209</v>
       </c>
       <c r="R49" t="n">
-        <v>7063450</v>
+        <v>7063388</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5738,6 +5768,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5764,10 +5799,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122735805</v>
+        <v>122733946</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>74858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,39 +5815,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>542199</v>
+        <v>541887</v>
       </c>
       <c r="R50" t="n">
-        <v>7063483</v>
+        <v>7063133</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5845,11 +5875,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5876,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122733746</v>
+        <v>122734184</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>97322</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5892,39 +5917,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541904</v>
+        <v>541962</v>
       </c>
       <c r="R51" t="n">
-        <v>7063170</v>
+        <v>7063054</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5983,10 +6003,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734693</v>
+        <v>122734191</v>
       </c>
       <c r="B52" t="n">
-        <v>90952</v>
+        <v>79850</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5999,21 +6019,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6023,10 +6043,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>542111</v>
+        <v>541959</v>
       </c>
       <c r="R52" t="n">
-        <v>7063060</v>
+        <v>7063011</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6085,10 +6105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122735414</v>
+        <v>122735308</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6101,39 +6121,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542209</v>
+        <v>542199</v>
       </c>
       <c r="R53" t="n">
-        <v>7063388</v>
+        <v>7063368</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6166,11 +6181,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6197,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122735437</v>
+        <v>122735193</v>
       </c>
       <c r="B54" t="n">
-        <v>79875</v>
+        <v>90920</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6213,21 +6223,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6237,10 +6247,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542207</v>
+        <v>542209</v>
       </c>
       <c r="R54" t="n">
-        <v>7063420</v>
+        <v>7063318</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6299,10 +6309,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122734876</v>
+        <v>122734661</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>90920</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6311,25 +6321,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6339,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542150</v>
+        <v>542103</v>
       </c>
       <c r="R55" t="n">
-        <v>7063210</v>
+        <v>7063058</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6404,7 +6414,7 @@
         <v>122734167</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6503,10 +6513,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734127</v>
+        <v>122734737</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>56691</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6515,38 +6525,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541949</v>
+        <v>542156</v>
       </c>
       <c r="R57" t="n">
-        <v>7063047</v>
+        <v>7063148</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6605,10 +6620,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122734191</v>
+        <v>122733400</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6617,38 +6632,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541959</v>
+        <v>541821</v>
       </c>
       <c r="R58" t="n">
-        <v>7063011</v>
+        <v>7063185</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6707,10 +6726,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122733611</v>
+        <v>122734433</v>
       </c>
       <c r="B59" t="n">
-        <v>56688</v>
+        <v>79850</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6719,43 +6738,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541894</v>
+        <v>542016</v>
       </c>
       <c r="R59" t="n">
-        <v>7063219</v>
+        <v>7063029</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6814,10 +6828,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122734679</v>
+        <v>122735437</v>
       </c>
       <c r="B60" t="n">
-        <v>56680</v>
+        <v>79878</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6826,43 +6840,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542110</v>
+        <v>542207</v>
       </c>
       <c r="R60" t="n">
-        <v>7063060</v>
+        <v>7063420</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6921,10 +6930,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122734232</v>
+        <v>122734614</v>
       </c>
       <c r="B61" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6937,21 +6946,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6961,10 +6970,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541952</v>
+        <v>542075</v>
       </c>
       <c r="R61" t="n">
-        <v>7063000</v>
+        <v>7063031</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7023,10 +7032,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122734570</v>
+        <v>122733821</v>
       </c>
       <c r="B62" t="n">
-        <v>90963</v>
+        <v>78769</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7035,38 +7044,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>542057</v>
+        <v>541894</v>
       </c>
       <c r="R62" t="n">
-        <v>7063036</v>
+        <v>7063121</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7125,10 +7139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122734737</v>
+        <v>122733626</v>
       </c>
       <c r="B63" t="n">
-        <v>56688</v>
+        <v>79850</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7137,43 +7151,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542156</v>
+        <v>541894</v>
       </c>
       <c r="R63" t="n">
-        <v>7063148</v>
+        <v>7063219</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7232,10 +7241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122740383</v>
+        <v>122733445</v>
       </c>
       <c r="B64" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7272,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542117</v>
+        <v>541842</v>
       </c>
       <c r="R64" t="n">
-        <v>7063503</v>
+        <v>7063190</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7334,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122733654</v>
+        <v>122734876</v>
       </c>
       <c r="B65" t="n">
-        <v>79718</v>
+        <v>79850</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7346,41 +7355,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541896</v>
+        <v>542150</v>
       </c>
       <c r="R65" t="n">
-        <v>7063207</v>
+        <v>7063210</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7421,7 +7427,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7440,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122733497</v>
+        <v>122735524</v>
       </c>
       <c r="B66" t="n">
-        <v>56688</v>
+        <v>79879</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7456,39 +7461,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541868</v>
+        <v>542224</v>
       </c>
       <c r="R66" t="n">
-        <v>7063207</v>
+        <v>7063455</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122734570</v>
+        <v>122733445</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>90922</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542057</v>
+        <v>541842</v>
       </c>
       <c r="R14" t="n">
-        <v>7063036</v>
+        <v>7063190</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122734709</v>
+        <v>122735414</v>
       </c>
       <c r="B15" t="n">
-        <v>91400</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,38 +2147,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542116</v>
+        <v>542209</v>
       </c>
       <c r="R15" t="n">
-        <v>7063065</v>
+        <v>7063388</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2211,6 +2216,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122734524</v>
+        <v>122734480</v>
       </c>
       <c r="B16" t="n">
-        <v>79850</v>
+        <v>90968</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,25 +2259,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542051</v>
+        <v>542012</v>
       </c>
       <c r="R16" t="n">
-        <v>7063037</v>
+        <v>7063013</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2339,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733573</v>
+        <v>122734232</v>
       </c>
       <c r="B17" t="n">
-        <v>56691</v>
+        <v>79888</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,39 +2365,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541859</v>
+        <v>541952</v>
       </c>
       <c r="R17" t="n">
-        <v>7063245</v>
+        <v>7063000</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2446,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122734998</v>
+        <v>122735437</v>
       </c>
       <c r="B18" t="n">
-        <v>57634</v>
+        <v>79880</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,43 +2463,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542180</v>
+        <v>542207</v>
       </c>
       <c r="R18" t="n">
-        <v>7063280</v>
+        <v>7063420</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122735254</v>
+        <v>122733654</v>
       </c>
       <c r="B19" t="n">
-        <v>79850</v>
+        <v>79723</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2565,38 +2565,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542200</v>
+        <v>541896</v>
       </c>
       <c r="R19" t="n">
-        <v>7063362</v>
+        <v>7063207</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2637,6 +2640,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2655,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122734559</v>
+        <v>122734549</v>
       </c>
       <c r="B20" t="n">
-        <v>90920</v>
+        <v>56081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2667,28 +2671,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
@@ -2757,7 +2766,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122733623</v>
+        <v>122733573</v>
       </c>
       <c r="B21" t="n">
         <v>56691</v>
@@ -2802,10 +2811,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541894</v>
+        <v>541859</v>
       </c>
       <c r="R21" t="n">
-        <v>7063219</v>
+        <v>7063245</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2864,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122735145</v>
+        <v>122734737</v>
       </c>
       <c r="B22" t="n">
-        <v>90955</v>
+        <v>56691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,38 +2885,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542201</v>
+        <v>542156</v>
       </c>
       <c r="R22" t="n">
-        <v>7063315</v>
+        <v>7063148</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2966,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122733412</v>
+        <v>122734679</v>
       </c>
       <c r="B23" t="n">
-        <v>79850</v>
+        <v>56683</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2982,34 +2996,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541827</v>
+        <v>542110</v>
       </c>
       <c r="R23" t="n">
-        <v>7063182</v>
+        <v>7063060</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3068,10 +3087,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122733348</v>
+        <v>122733859</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>90957</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,39 +3103,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541796</v>
+        <v>541895</v>
       </c>
       <c r="R24" t="n">
-        <v>7063200</v>
+        <v>7063121</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3149,11 +3163,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122733746</v>
+        <v>122734709</v>
       </c>
       <c r="B25" t="n">
-        <v>56691</v>
+        <v>91402</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,43 +3201,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541904</v>
+        <v>542116</v>
       </c>
       <c r="R25" t="n">
-        <v>7063170</v>
+        <v>7063065</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3287,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122734232</v>
+        <v>122734191</v>
       </c>
       <c r="B26" t="n">
-        <v>79886</v>
+        <v>79852</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3299,25 +3303,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3327,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541952</v>
+        <v>541959</v>
       </c>
       <c r="R26" t="n">
-        <v>7063000</v>
+        <v>7063011</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3389,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122734094</v>
+        <v>122734495</v>
       </c>
       <c r="B27" t="n">
-        <v>57497</v>
+        <v>79756</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3401,43 +3405,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541918</v>
+        <v>542019</v>
       </c>
       <c r="R27" t="n">
-        <v>7063050</v>
+        <v>7063019</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3496,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122735491</v>
+        <v>122734589</v>
       </c>
       <c r="B28" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3536,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542222</v>
+        <v>542061</v>
       </c>
       <c r="R28" t="n">
-        <v>7063450</v>
+        <v>7063040</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3598,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122734884</v>
+        <v>122734693</v>
       </c>
       <c r="B29" t="n">
-        <v>90920</v>
+        <v>90957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3610,25 +3609,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3638,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542151</v>
+        <v>542111</v>
       </c>
       <c r="R29" t="n">
-        <v>7063216</v>
+        <v>7063060</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3700,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122734589</v>
+        <v>122735514</v>
       </c>
       <c r="B30" t="n">
-        <v>79850</v>
+        <v>79887</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3712,25 +3711,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,10 +3739,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542061</v>
+        <v>542225</v>
       </c>
       <c r="R30" t="n">
-        <v>7063040</v>
+        <v>7063451</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3802,10 +3801,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122733223</v>
+        <v>122735491</v>
       </c>
       <c r="B31" t="n">
-        <v>56691</v>
+        <v>79852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3814,43 +3813,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541808</v>
+        <v>542222</v>
       </c>
       <c r="R31" t="n">
-        <v>7063277</v>
+        <v>7063450</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3909,10 +3903,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122734495</v>
+        <v>122733611</v>
       </c>
       <c r="B32" t="n">
-        <v>79754</v>
+        <v>56691</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3925,34 +3919,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542019</v>
+        <v>541894</v>
       </c>
       <c r="R32" t="n">
-        <v>7063019</v>
+        <v>7063219</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4011,10 +4010,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122740383</v>
+        <v>122734884</v>
       </c>
       <c r="B33" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4051,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542117</v>
+        <v>542151</v>
       </c>
       <c r="R33" t="n">
-        <v>7063503</v>
+        <v>7063216</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4113,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122734127</v>
+        <v>122733368</v>
       </c>
       <c r="B34" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4129,34 +4128,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541949</v>
+        <v>541796</v>
       </c>
       <c r="R34" t="n">
-        <v>7063047</v>
+        <v>7063200</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4189,6 +4193,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4215,10 +4224,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122734693</v>
+        <v>122734998</v>
       </c>
       <c r="B35" t="n">
-        <v>90955</v>
+        <v>57634</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4231,34 +4240,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542111</v>
+        <v>542180</v>
       </c>
       <c r="R35" t="n">
-        <v>7063060</v>
+        <v>7063280</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4317,10 +4331,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122735552</v>
+        <v>122733400</v>
       </c>
       <c r="B36" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4329,31 +4343,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4362,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542188</v>
+        <v>541821</v>
       </c>
       <c r="R36" t="n">
-        <v>7063472</v>
+        <v>7063185</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4424,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122735514</v>
+        <v>122734184</v>
       </c>
       <c r="B37" t="n">
-        <v>79885</v>
+        <v>97324</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4440,21 +4453,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4464,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542225</v>
+        <v>541962</v>
       </c>
       <c r="R37" t="n">
-        <v>7063451</v>
+        <v>7063054</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4526,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122733859</v>
+        <v>122735805</v>
       </c>
       <c r="B38" t="n">
-        <v>90955</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4542,34 +4555,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541895</v>
+        <v>542199</v>
       </c>
       <c r="R38" t="n">
-        <v>7063121</v>
+        <v>7063483</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4602,6 +4620,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4628,10 +4651,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122734679</v>
+        <v>122735524</v>
       </c>
       <c r="B39" t="n">
-        <v>56683</v>
+        <v>79881</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4640,43 +4663,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542110</v>
+        <v>542224</v>
       </c>
       <c r="R39" t="n">
-        <v>7063060</v>
+        <v>7063455</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4735,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122734625</v>
+        <v>122734127</v>
       </c>
       <c r="B40" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4775,10 +4793,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542072</v>
+        <v>541949</v>
       </c>
       <c r="R40" t="n">
-        <v>7063043</v>
+        <v>7063047</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4837,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122735805</v>
+        <v>122735145</v>
       </c>
       <c r="B41" t="n">
-        <v>57481</v>
+        <v>90957</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,39 +4871,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542199</v>
+        <v>542201</v>
       </c>
       <c r="R41" t="n">
-        <v>7063483</v>
+        <v>7063315</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4918,11 +4931,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4949,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122733598</v>
+        <v>122734167</v>
       </c>
       <c r="B42" t="n">
-        <v>56691</v>
+        <v>79852</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4961,43 +4969,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541891</v>
+        <v>541962</v>
       </c>
       <c r="R42" t="n">
-        <v>7063227</v>
+        <v>7063054</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5056,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122733497</v>
+        <v>122735254</v>
       </c>
       <c r="B43" t="n">
-        <v>56691</v>
+        <v>79852</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5068,43 +5071,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541868</v>
+        <v>542200</v>
       </c>
       <c r="R43" t="n">
-        <v>7063207</v>
+        <v>7063362</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5163,10 +5161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122733563</v>
+        <v>122733223</v>
       </c>
       <c r="B44" t="n">
-        <v>88306</v>
+        <v>56691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5175,38 +5173,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541868</v>
+        <v>541808</v>
       </c>
       <c r="R44" t="n">
-        <v>7063239</v>
+        <v>7063277</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5265,10 +5268,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122733654</v>
+        <v>122734524</v>
       </c>
       <c r="B45" t="n">
-        <v>79721</v>
+        <v>79852</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5277,41 +5280,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>389</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541896</v>
+        <v>542051</v>
       </c>
       <c r="R45" t="n">
-        <v>7063207</v>
+        <v>7063037</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5352,7 +5352,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5371,10 +5370,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122734549</v>
+        <v>122733563</v>
       </c>
       <c r="B46" t="n">
-        <v>56081</v>
+        <v>88308</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5387,39 +5386,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>206004</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542051</v>
+        <v>541868</v>
       </c>
       <c r="R46" t="n">
-        <v>7063037</v>
+        <v>7063239</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5478,10 +5472,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122734480</v>
+        <v>122733497</v>
       </c>
       <c r="B47" t="n">
-        <v>90966</v>
+        <v>56691</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5494,34 +5488,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542012</v>
+        <v>541868</v>
       </c>
       <c r="R47" t="n">
-        <v>7063013</v>
+        <v>7063207</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5580,10 +5579,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122734932</v>
+        <v>122733946</v>
       </c>
       <c r="B48" t="n">
-        <v>78769</v>
+        <v>74858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5596,21 +5595,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5620,10 +5619,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>542178</v>
+        <v>541887</v>
       </c>
       <c r="R48" t="n">
-        <v>7063224</v>
+        <v>7063133</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5656,11 +5655,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5687,10 +5681,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122735414</v>
+        <v>122734094</v>
       </c>
       <c r="B49" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5703,16 +5697,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5723,7 +5717,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5732,10 +5726,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>542209</v>
+        <v>541918</v>
       </c>
       <c r="R49" t="n">
-        <v>7063388</v>
+        <v>7063050</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5768,11 +5762,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5799,10 +5788,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122733946</v>
+        <v>122733821</v>
       </c>
       <c r="B50" t="n">
-        <v>74858</v>
+        <v>78771</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5815,34 +5804,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541887</v>
+        <v>541894</v>
       </c>
       <c r="R50" t="n">
-        <v>7063133</v>
+        <v>7063121</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5901,10 +5895,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122734184</v>
+        <v>122734625</v>
       </c>
       <c r="B51" t="n">
-        <v>97322</v>
+        <v>79852</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,25 +5907,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5941,10 +5935,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541962</v>
+        <v>542072</v>
       </c>
       <c r="R51" t="n">
-        <v>7063054</v>
+        <v>7063043</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6003,10 +5997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122734191</v>
+        <v>122735308</v>
       </c>
       <c r="B52" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6043,10 +6037,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541959</v>
+        <v>542199</v>
       </c>
       <c r="R52" t="n">
-        <v>7063011</v>
+        <v>7063368</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6105,10 +6099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122735308</v>
+        <v>122734661</v>
       </c>
       <c r="B53" t="n">
-        <v>79850</v>
+        <v>90922</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6117,25 +6111,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6145,10 +6139,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542199</v>
+        <v>542103</v>
       </c>
       <c r="R53" t="n">
-        <v>7063368</v>
+        <v>7063058</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6210,7 +6204,7 @@
         <v>122735193</v>
       </c>
       <c r="B54" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6309,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122734661</v>
+        <v>122734433</v>
       </c>
       <c r="B55" t="n">
-        <v>90920</v>
+        <v>79852</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6321,25 +6315,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6349,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542103</v>
+        <v>542016</v>
       </c>
       <c r="R55" t="n">
-        <v>7063058</v>
+        <v>7063029</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6411,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122734167</v>
+        <v>122734614</v>
       </c>
       <c r="B56" t="n">
-        <v>79850</v>
+        <v>79887</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6423,25 +6417,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6451,10 +6445,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541962</v>
+        <v>542075</v>
       </c>
       <c r="R56" t="n">
-        <v>7063054</v>
+        <v>7063031</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6513,7 +6507,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122734737</v>
+        <v>122733746</v>
       </c>
       <c r="B57" t="n">
         <v>56691</v>
@@ -6558,10 +6552,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>542156</v>
+        <v>541904</v>
       </c>
       <c r="R57" t="n">
-        <v>7063148</v>
+        <v>7063170</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6620,10 +6614,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122733400</v>
+        <v>122733626</v>
       </c>
       <c r="B58" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6632,42 +6626,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541821</v>
+        <v>541894</v>
       </c>
       <c r="R58" t="n">
-        <v>7063185</v>
+        <v>7063219</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6726,10 +6716,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122734433</v>
+        <v>122734570</v>
       </c>
       <c r="B59" t="n">
-        <v>79850</v>
+        <v>90968</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6738,25 +6728,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6766,10 +6756,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>542016</v>
+        <v>542057</v>
       </c>
       <c r="R59" t="n">
-        <v>7063029</v>
+        <v>7063036</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6828,10 +6818,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122735437</v>
+        <v>122734932</v>
       </c>
       <c r="B60" t="n">
-        <v>79878</v>
+        <v>78771</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6840,25 +6830,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6868,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>542207</v>
+        <v>542178</v>
       </c>
       <c r="R60" t="n">
-        <v>7063420</v>
+        <v>7063224</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6904,6 +6894,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt (hela berget)</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6930,10 +6925,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122734614</v>
+        <v>122734876</v>
       </c>
       <c r="B61" t="n">
-        <v>79885</v>
+        <v>79852</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6942,25 +6937,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6970,10 +6965,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>542075</v>
+        <v>542150</v>
       </c>
       <c r="R61" t="n">
-        <v>7063031</v>
+        <v>7063210</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7032,10 +7027,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122733821</v>
+        <v>122733412</v>
       </c>
       <c r="B62" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7048,39 +7043,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541894</v>
+        <v>541827</v>
       </c>
       <c r="R62" t="n">
-        <v>7063121</v>
+        <v>7063182</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7139,10 +7129,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122733626</v>
+        <v>122733598</v>
       </c>
       <c r="B63" t="n">
-        <v>79850</v>
+        <v>56691</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7151,38 +7141,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541894</v>
+        <v>541891</v>
       </c>
       <c r="R63" t="n">
-        <v>7063219</v>
+        <v>7063227</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7241,10 +7236,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122733445</v>
+        <v>122740383</v>
       </c>
       <c r="B64" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7281,10 +7276,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541842</v>
+        <v>542117</v>
       </c>
       <c r="R64" t="n">
-        <v>7063190</v>
+        <v>7063503</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7343,10 +7338,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122734876</v>
+        <v>122734559</v>
       </c>
       <c r="B65" t="n">
-        <v>79850</v>
+        <v>90922</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7355,25 +7350,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7383,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542150</v>
+        <v>542051</v>
       </c>
       <c r="R65" t="n">
-        <v>7063210</v>
+        <v>7063037</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7445,10 +7440,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122735524</v>
+        <v>122735552</v>
       </c>
       <c r="B66" t="n">
-        <v>79879</v>
+        <v>56691</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7461,34 +7456,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>542224</v>
+        <v>542188</v>
       </c>
       <c r="R66" t="n">
-        <v>7063455</v>
+        <v>7063472</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -7550,7 +7550,7 @@
         <v>130153725</v>
       </c>
       <c r="B67" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>130153783</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>130153766</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>130153494</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -7652,7 +7652,7 @@
         <v>130153783</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>130153494</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 3157-2025 artfynd.xlsx
+++ b/artfynd/A 3157-2025 artfynd.xlsx
@@ -7550,7 +7550,7 @@
         <v>130153725</v>
       </c>
       <c r="B67" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>130153783</v>
       </c>
       <c r="B68" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>130153766</v>
       </c>
       <c r="B69" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>130153494</v>
       </c>
       <c r="B70" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
